--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3185,13 +3185,13 @@
     <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
+    <t>[Donnée restreinte] : Date à partir de laquelle le professionnel exerce cette profession (dateEffetExercice).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
+  </si>
+  <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.issuer</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,8 +872,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutInscription</t>
@@ -6215,7 +6215,7 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>129</v>
@@ -6242,7 +6242,7 @@
         <v>83</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>83</v>
@@ -6347,7 +6347,7 @@
         <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>129</v>
@@ -6607,7 +6607,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>129</v>
@@ -6867,7 +6867,7 @@
         <v>100</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>112</v>
@@ -6999,7 +6999,7 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>129</v>
@@ -7259,7 +7259,7 @@
         <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>129</v>
@@ -7519,7 +7519,7 @@
         <v>100</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>112</v>
@@ -7651,7 +7651,7 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>129</v>
@@ -7911,7 +7911,7 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>129</v>
@@ -8173,7 +8173,7 @@
         <v>100</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>112</v>
@@ -8435,7 +8435,7 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>129</v>
@@ -8462,7 +8462,7 @@
         <v>83</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>83</v>
@@ -8833,7 +8833,7 @@
         <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>129</v>
@@ -9093,7 +9093,7 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>129</v>
@@ -9353,7 +9353,7 @@
         <v>100</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>112</v>
@@ -9485,7 +9485,7 @@
         <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>129</v>
@@ -9745,7 +9745,7 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>129</v>
@@ -10005,7 +10005,7 @@
         <v>100</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>112</v>
@@ -10137,7 +10137,7 @@
         <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>129</v>
@@ -10397,7 +10397,7 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>129</v>
@@ -10659,7 +10659,7 @@
         <v>100</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>112</v>
@@ -10921,7 +10921,7 @@
         <v>100</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>112</v>
@@ -11315,7 +11315,7 @@
         <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>129</v>
@@ -11342,7 +11342,7 @@
         <v>83</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS62" t="s" s="2">
         <v>83</v>
@@ -11447,7 +11447,7 @@
         <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>129</v>
@@ -11707,7 +11707,7 @@
         <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>129</v>
@@ -11967,7 +11967,7 @@
         <v>100</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>112</v>
@@ -12099,7 +12099,7 @@
         <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>129</v>
@@ -12359,7 +12359,7 @@
         <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>129</v>
@@ -12621,7 +12621,7 @@
         <v>100</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>112</v>
@@ -12883,7 +12883,7 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>129</v>
@@ -12910,7 +12910,7 @@
         <v>83</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS74" t="s" s="2">
         <v>83</v>
@@ -13281,7 +13281,7 @@
         <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>129</v>
@@ -13541,7 +13541,7 @@
         <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>129</v>
@@ -13801,7 +13801,7 @@
         <v>100</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>112</v>
@@ -13933,7 +13933,7 @@
         <v>85</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>129</v>
@@ -14193,7 +14193,7 @@
         <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>129</v>
@@ -14453,7 +14453,7 @@
         <v>100</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>112</v>
@@ -14715,7 +14715,7 @@
         <v>100</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>112</v>
@@ -26601,7 +26601,7 @@
         <v>85</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>129</v>
@@ -26628,7 +26628,7 @@
         <v>83</v>
       </c>
       <c r="AR178" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS178" t="s" s="2">
         <v>83</v>
@@ -26733,7 +26733,7 @@
         <v>85</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>129</v>
@@ -26993,7 +26993,7 @@
         <v>85</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>129</v>
@@ -27253,7 +27253,7 @@
         <v>100</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>112</v>
@@ -27385,7 +27385,7 @@
         <v>85</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>129</v>
@@ -27645,7 +27645,7 @@
         <v>85</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>129</v>
@@ -27905,7 +27905,7 @@
         <v>100</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>112</v>
@@ -28037,7 +28037,7 @@
         <v>85</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>129</v>
@@ -28297,7 +28297,7 @@
         <v>85</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>129</v>
@@ -28557,7 +28557,7 @@
         <v>100</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>112</v>
@@ -28819,7 +28819,7 @@
         <v>100</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>112</v>
@@ -29475,7 +29475,7 @@
         <v>85</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>129</v>
@@ -29502,7 +29502,7 @@
         <v>83</v>
       </c>
       <c r="AR200" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS200" t="s" s="2">
         <v>83</v>
@@ -29607,7 +29607,7 @@
         <v>85</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>112</v>
@@ -29741,7 +29741,7 @@
         <v>85</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>112</v>
@@ -29875,7 +29875,7 @@
         <v>85</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>112</v>
@@ -30009,7 +30009,7 @@
         <v>100</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>112</v>
@@ -30403,7 +30403,7 @@
         <v>85</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ207" t="s" s="2">
         <v>129</v>
@@ -30430,7 +30430,7 @@
         <v>83</v>
       </c>
       <c r="AR207" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS207" t="s" s="2">
         <v>83</v>
@@ -31849,7 +31849,7 @@
         <v>85</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>129</v>
@@ -31876,7 +31876,7 @@
         <v>83</v>
       </c>
       <c r="AR218" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS218" t="s" s="2">
         <v>83</v>
@@ -31981,7 +31981,7 @@
         <v>85</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ219" t="s" s="2">
         <v>112</v>
@@ -32115,7 +32115,7 @@
         <v>85</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ220" t="s" s="2">
         <v>112</v>
@@ -32249,7 +32249,7 @@
         <v>85</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>112</v>
@@ -32383,7 +32383,7 @@
         <v>100</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>112</v>
@@ -32777,7 +32777,7 @@
         <v>85</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>129</v>
@@ -32804,7 +32804,7 @@
         <v>83</v>
       </c>
       <c r="AR225" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS225" t="s" s="2">
         <v>83</v>
@@ -34223,7 +34223,7 @@
         <v>85</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>129</v>
@@ -34250,7 +34250,7 @@
         <v>83</v>
       </c>
       <c r="AR236" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS236" t="s" s="2">
         <v>83</v>
@@ -34355,7 +34355,7 @@
         <v>85</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>112</v>
@@ -34489,7 +34489,7 @@
         <v>85</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>112</v>
@@ -34623,7 +34623,7 @@
         <v>85</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>112</v>
@@ -34757,7 +34757,7 @@
         <v>100</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>112</v>
@@ -35151,7 +35151,7 @@
         <v>85</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>129</v>
@@ -35178,7 +35178,7 @@
         <v>83</v>
       </c>
       <c r="AR243" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS243" t="s" s="2">
         <v>83</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,8 +872,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>dateDebutInscription</t>
@@ -6215,7 +6215,7 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>129</v>
@@ -6242,7 +6242,7 @@
         <v>83</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>83</v>
@@ -6347,7 +6347,7 @@
         <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>129</v>
@@ -6607,7 +6607,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>129</v>
@@ -6867,7 +6867,7 @@
         <v>100</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>112</v>
@@ -6999,7 +6999,7 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>129</v>
@@ -7259,7 +7259,7 @@
         <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>129</v>
@@ -7519,7 +7519,7 @@
         <v>100</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>112</v>
@@ -7651,7 +7651,7 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>129</v>
@@ -7911,7 +7911,7 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>129</v>
@@ -8173,7 +8173,7 @@
         <v>100</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>112</v>
@@ -8435,7 +8435,7 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>129</v>
@@ -8462,7 +8462,7 @@
         <v>83</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>83</v>
@@ -8833,7 +8833,7 @@
         <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>129</v>
@@ -9093,7 +9093,7 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>129</v>
@@ -9353,7 +9353,7 @@
         <v>100</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>112</v>
@@ -9485,7 +9485,7 @@
         <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>129</v>
@@ -9745,7 +9745,7 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>129</v>
@@ -10005,7 +10005,7 @@
         <v>100</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>112</v>
@@ -10137,7 +10137,7 @@
         <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>129</v>
@@ -10397,7 +10397,7 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>129</v>
@@ -10659,7 +10659,7 @@
         <v>100</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>112</v>
@@ -10921,7 +10921,7 @@
         <v>100</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>112</v>
@@ -11315,7 +11315,7 @@
         <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>129</v>
@@ -11342,7 +11342,7 @@
         <v>83</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS62" t="s" s="2">
         <v>83</v>
@@ -11447,7 +11447,7 @@
         <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>129</v>
@@ -11707,7 +11707,7 @@
         <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>129</v>
@@ -11967,7 +11967,7 @@
         <v>100</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>112</v>
@@ -12099,7 +12099,7 @@
         <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>129</v>
@@ -12359,7 +12359,7 @@
         <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>129</v>
@@ -12621,7 +12621,7 @@
         <v>100</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>112</v>
@@ -12883,7 +12883,7 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>129</v>
@@ -12910,7 +12910,7 @@
         <v>83</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS74" t="s" s="2">
         <v>83</v>
@@ -13281,7 +13281,7 @@
         <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>129</v>
@@ -13541,7 +13541,7 @@
         <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>129</v>
@@ -13801,7 +13801,7 @@
         <v>100</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>112</v>
@@ -13933,7 +13933,7 @@
         <v>85</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>129</v>
@@ -14193,7 +14193,7 @@
         <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>129</v>
@@ -14453,7 +14453,7 @@
         <v>100</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>112</v>
@@ -14715,7 +14715,7 @@
         <v>100</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>112</v>
@@ -26601,7 +26601,7 @@
         <v>85</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>129</v>
@@ -26628,7 +26628,7 @@
         <v>83</v>
       </c>
       <c r="AR178" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS178" t="s" s="2">
         <v>83</v>
@@ -26733,7 +26733,7 @@
         <v>85</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>129</v>
@@ -26993,7 +26993,7 @@
         <v>85</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>129</v>
@@ -27253,7 +27253,7 @@
         <v>100</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>112</v>
@@ -27385,7 +27385,7 @@
         <v>85</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>129</v>
@@ -27645,7 +27645,7 @@
         <v>85</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>129</v>
@@ -27905,7 +27905,7 @@
         <v>100</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>112</v>
@@ -28037,7 +28037,7 @@
         <v>85</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>129</v>
@@ -28297,7 +28297,7 @@
         <v>85</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>129</v>
@@ -28557,7 +28557,7 @@
         <v>100</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>112</v>
@@ -28819,7 +28819,7 @@
         <v>100</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>112</v>
@@ -29475,7 +29475,7 @@
         <v>85</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>129</v>
@@ -29502,7 +29502,7 @@
         <v>83</v>
       </c>
       <c r="AR200" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS200" t="s" s="2">
         <v>83</v>
@@ -29607,7 +29607,7 @@
         <v>85</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>112</v>
@@ -29741,7 +29741,7 @@
         <v>85</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>112</v>
@@ -29875,7 +29875,7 @@
         <v>85</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>112</v>
@@ -30009,7 +30009,7 @@
         <v>100</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>112</v>
@@ -30403,7 +30403,7 @@
         <v>85</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ207" t="s" s="2">
         <v>129</v>
@@ -30430,7 +30430,7 @@
         <v>83</v>
       </c>
       <c r="AR207" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS207" t="s" s="2">
         <v>83</v>
@@ -31849,7 +31849,7 @@
         <v>85</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>129</v>
@@ -31876,7 +31876,7 @@
         <v>83</v>
       </c>
       <c r="AR218" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS218" t="s" s="2">
         <v>83</v>
@@ -31981,7 +31981,7 @@
         <v>85</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ219" t="s" s="2">
         <v>112</v>
@@ -32115,7 +32115,7 @@
         <v>85</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ220" t="s" s="2">
         <v>112</v>
@@ -32249,7 +32249,7 @@
         <v>85</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>112</v>
@@ -32383,7 +32383,7 @@
         <v>100</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>112</v>
@@ -32777,7 +32777,7 @@
         <v>85</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>129</v>
@@ -32804,7 +32804,7 @@
         <v>83</v>
       </c>
       <c r="AR225" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS225" t="s" s="2">
         <v>83</v>
@@ -34223,7 +34223,7 @@
         <v>85</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>129</v>
@@ -34250,7 +34250,7 @@
         <v>83</v>
       </c>
       <c r="AR236" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS236" t="s" s="2">
         <v>83</v>
@@ -34355,7 +34355,7 @@
         <v>85</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>112</v>
@@ -34489,7 +34489,7 @@
         <v>85</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>112</v>
@@ -34623,7 +34623,7 @@
         <v>85</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>112</v>
@@ -34757,7 +34757,7 @@
         <v>100</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>112</v>
@@ -35151,7 +35151,7 @@
         <v>85</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>129</v>
@@ -35178,7 +35178,7 @@
         <v>83</v>
       </c>
       <c r="AR243" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="AS243" t="s" s="2">
         <v>83</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="917">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,8 +872,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutInscription</t>
@@ -1594,9 +1594,13 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+  </si>
+  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1656,7 +1660,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="RPPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1665,7 +1669,7 @@
     <t>Practitioner.identifier:rpps.system</t>
   </si>
   <si>
-    <t>http://rpps.esante.gouv.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:rpps.value</t>
@@ -1700,7 +1704,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="ADELI"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1709,7 +1713,7 @@
     <t>Practitioner.identifier:adeli.system</t>
   </si>
   <si>
-    <t>http://adeli.esante.gouv.fr</t>
+    <t>https://adeli.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:adeli.value</t>
@@ -6215,7 +6219,7 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>129</v>
@@ -6242,7 +6246,7 @@
         <v>83</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>83</v>
@@ -6347,7 +6351,7 @@
         <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>129</v>
@@ -6607,7 +6611,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>129</v>
@@ -6867,7 +6871,7 @@
         <v>100</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>112</v>
@@ -6999,7 +7003,7 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>129</v>
@@ -7259,7 +7263,7 @@
         <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>129</v>
@@ -7519,7 +7523,7 @@
         <v>100</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>112</v>
@@ -7651,7 +7655,7 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>129</v>
@@ -7911,7 +7915,7 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>129</v>
@@ -8173,7 +8177,7 @@
         <v>100</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>112</v>
@@ -8435,7 +8439,7 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>129</v>
@@ -8462,7 +8466,7 @@
         <v>83</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>83</v>
@@ -8833,7 +8837,7 @@
         <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>129</v>
@@ -9093,7 +9097,7 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>129</v>
@@ -9353,7 +9357,7 @@
         <v>100</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>112</v>
@@ -9485,7 +9489,7 @@
         <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>129</v>
@@ -9745,7 +9749,7 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>129</v>
@@ -10005,7 +10009,7 @@
         <v>100</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>112</v>
@@ -10137,7 +10141,7 @@
         <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>129</v>
@@ -10397,7 +10401,7 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>129</v>
@@ -10659,7 +10663,7 @@
         <v>100</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>112</v>
@@ -10921,7 +10925,7 @@
         <v>100</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>112</v>
@@ -11315,7 +11319,7 @@
         <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>129</v>
@@ -11342,7 +11346,7 @@
         <v>83</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS62" t="s" s="2">
         <v>83</v>
@@ -11447,7 +11451,7 @@
         <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>129</v>
@@ -11707,7 +11711,7 @@
         <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>129</v>
@@ -11967,7 +11971,7 @@
         <v>100</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>112</v>
@@ -12099,7 +12103,7 @@
         <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>129</v>
@@ -12359,7 +12363,7 @@
         <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>129</v>
@@ -12621,7 +12625,7 @@
         <v>100</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>112</v>
@@ -12883,7 +12887,7 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>129</v>
@@ -12910,7 +12914,7 @@
         <v>83</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS74" t="s" s="2">
         <v>83</v>
@@ -13281,7 +13285,7 @@
         <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>129</v>
@@ -13541,7 +13545,7 @@
         <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>129</v>
@@ -13801,7 +13805,7 @@
         <v>100</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>112</v>
@@ -13933,7 +13937,7 @@
         <v>85</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>129</v>
@@ -14193,7 +14197,7 @@
         <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>129</v>
@@ -14453,7 +14457,7 @@
         <v>100</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>112</v>
@@ -14715,7 +14719,7 @@
         <v>100</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>112</v>
@@ -18354,7 +18358,7 @@
         <v>243</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>402</v>
+        <v>510</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>403</v>
@@ -18373,7 +18377,7 @@
         <v>83</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>83</v>
@@ -18391,10 +18395,10 @@
         <v>167</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -18459,7 +18463,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>467</v>
@@ -18491,7 +18495,7 @@
         <v>468</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>470</v>
@@ -18507,7 +18511,7 @@
         <v>83</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>472</v>
@@ -18593,7 +18597,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>477</v>
@@ -18622,7 +18626,7 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>479</v>
@@ -18725,7 +18729,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>486</v>
@@ -18855,7 +18859,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>493</v>
@@ -18987,13 +18991,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>379</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>83</v>
@@ -19018,7 +19022,7 @@
         <v>380</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>382</v>
@@ -19121,7 +19125,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>390</v>
@@ -19251,7 +19255,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>391</v>
@@ -19383,7 +19387,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>392</v>
@@ -19517,7 +19521,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>401</v>
@@ -19546,7 +19550,7 @@
         <v>243</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>403</v>
@@ -19565,7 +19569,7 @@
         <v>83</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>83</v>
@@ -19583,10 +19587,10 @@
         <v>167</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
@@ -19651,7 +19655,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>467</v>
@@ -19683,7 +19687,7 @@
         <v>468</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>470</v>
@@ -19699,7 +19703,7 @@
         <v>83</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>472</v>
@@ -19785,7 +19789,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>477</v>
@@ -19917,7 +19921,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>486</v>
@@ -20047,7 +20051,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>493</v>
@@ -20179,13 +20183,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>379</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>83</v>
@@ -20210,7 +20214,7 @@
         <v>380</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>382</v>
@@ -20313,7 +20317,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>390</v>
@@ -20443,7 +20447,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>391</v>
@@ -20575,7 +20579,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>392</v>
@@ -20709,7 +20713,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>401</v>
@@ -20738,7 +20742,7 @@
         <v>243</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>403</v>
@@ -20757,7 +20761,7 @@
         <v>83</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>83</v>
@@ -20775,10 +20779,10 @@
         <v>167</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>83</v>
@@ -20843,7 +20847,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>467</v>
@@ -20875,7 +20879,7 @@
         <v>468</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>470</v>
@@ -20891,7 +20895,7 @@
         <v>83</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>472</v>
@@ -20977,7 +20981,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>477</v>
@@ -21109,7 +21113,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>486</v>
@@ -21239,7 +21243,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>493</v>
@@ -21371,10 +21375,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -21400,67 +21404,67 @@
         <v>311</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q139" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="R139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF139" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="P139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q139" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="R139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -21496,21 +21500,21 @@
         <v>83</v>
       </c>
       <c r="AR139" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AS139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT139" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21533,19 +21537,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -21594,7 +21598,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>84</v>
@@ -21627,13 +21631,13 @@
         <v>83</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AS140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AT140" t="s" s="2">
         <v>83</v>
@@ -21641,10 +21645,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21771,10 +21775,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21903,13 +21907,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="B143" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="C143" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>83</v>
@@ -21931,13 +21935,13 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -22035,10 +22039,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -22064,16 +22068,16 @@
         <v>185</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
@@ -22102,7 +22106,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>83</v>
@@ -22120,7 +22124,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>84</v>
@@ -22153,13 +22157,13 @@
         <v>83</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AS144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AT144" t="s" s="2">
         <v>83</v>
@@ -22167,10 +22171,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -22196,16 +22200,16 @@
         <v>114</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>83</v>
@@ -22254,7 +22258,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>84</v>
@@ -22287,10 +22291,10 @@
         <v>83</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AS145" t="s" s="2">
         <v>83</v>
@@ -22301,14 +22305,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -22330,13 +22334,13 @@
         <v>114</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -22386,7 +22390,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -22404,7 +22408,7 @@
         <v>83</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>83</v>
@@ -22419,13 +22423,13 @@
         <v>83</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AS146" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AT146" t="s" s="2">
         <v>83</v>
@@ -22433,14 +22437,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -22462,13 +22466,13 @@
         <v>114</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -22518,7 +22522,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>84</v>
@@ -22536,7 +22540,7 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>83</v>
@@ -22551,13 +22555,13 @@
         <v>83</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AS147" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AT147" t="s" s="2">
         <v>83</v>
@@ -22565,10 +22569,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22594,10 +22598,10 @@
         <v>114</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -22627,10 +22631,10 @@
         <v>167</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>83</v>
@@ -22648,7 +22652,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>84</v>
@@ -22681,13 +22685,13 @@
         <v>83</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AS148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AT148" t="s" s="2">
         <v>83</v>
@@ -22695,10 +22699,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22724,10 +22728,10 @@
         <v>114</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22757,10 +22761,10 @@
         <v>167</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>83</v>
@@ -22778,7 +22782,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -22796,7 +22800,7 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>83</v>
@@ -22811,10 +22815,10 @@
         <v>83</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AS149" t="s" s="2">
         <v>83</v>
@@ -22825,10 +22829,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22854,14 +22858,14 @@
         <v>263</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -22910,7 +22914,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>84</v>
@@ -22943,10 +22947,10 @@
         <v>83</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AS150" t="s" s="2">
         <v>492</v>
@@ -22957,10 +22961,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22983,19 +22987,19 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -23032,7 +23036,7 @@
         <v>83</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -23042,7 +23046,7 @@
         <v>127</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>84</v>
@@ -23054,7 +23058,7 @@
         <v>218</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>83</v>
@@ -23069,19 +23073,19 @@
         <v>83</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AS151" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AT151" t="s" s="2">
         <v>83</v>
@@ -23089,10 +23093,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -23219,10 +23223,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -23351,13 +23355,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="B154" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="C154" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>83</v>
@@ -23379,13 +23383,13 @@
         <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -23483,10 +23487,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23512,10 +23516,10 @@
         <v>185</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -23545,10 +23549,10 @@
         <v>246</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>83</v>
@@ -23566,7 +23570,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -23575,7 +23579,7 @@
         <v>100</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>112</v>
@@ -23599,13 +23603,13 @@
         <v>83</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AS155" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AT155" t="s" s="2">
         <v>83</v>
@@ -23613,10 +23617,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -23642,16 +23646,16 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
@@ -23700,7 +23704,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -23733,10 +23737,10 @@
         <v>83</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AR156" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AS156" t="s" s="2">
         <v>485</v>
@@ -23747,10 +23751,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23776,16 +23780,16 @@
         <v>185</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -23813,10 +23817,10 @@
         <v>246</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>83</v>
@@ -23834,7 +23838,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>84</v>
@@ -23867,13 +23871,13 @@
         <v>83</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AS157" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AT157" t="s" s="2">
         <v>83</v>
@@ -23881,10 +23885,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23907,16 +23911,16 @@
         <v>101</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -23966,7 +23970,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -24013,10 +24017,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -24042,10 +24046,10 @@
         <v>263</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -24096,7 +24100,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>84</v>
@@ -24132,7 +24136,7 @@
         <v>208</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AS159" t="s" s="2">
         <v>492</v>
@@ -24143,13 +24147,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>83</v>
@@ -24171,19 +24175,19 @@
         <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -24232,7 +24236,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>84</v>
@@ -24244,13 +24248,13 @@
         <v>218</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>83</v>
@@ -24265,13 +24269,13 @@
         <v>83</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AR160" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AS160" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AT160" t="s" s="2">
         <v>83</v>
@@ -24279,10 +24283,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -24305,19 +24309,19 @@
         <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -24366,7 +24370,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>84</v>
@@ -24393,19 +24397,19 @@
         <v>83</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AP161" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AS161" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AT161" t="s" s="2">
         <v>83</v>
@@ -24413,10 +24417,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24442,14 +24446,14 @@
         <v>185</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -24477,10 +24481,10 @@
         <v>246</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
@@ -24498,7 +24502,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>84</v>
@@ -24531,13 +24535,13 @@
         <v>83</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AS162" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AT162" t="s" s="2">
         <v>83</v>
@@ -24545,10 +24549,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -24571,17 +24575,17 @@
         <v>101</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -24630,7 +24634,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>84</v>
@@ -24663,13 +24667,13 @@
         <v>83</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AR163" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AS163" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AT163" t="s" s="2">
         <v>83</v>
@@ -24677,10 +24681,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24703,17 +24707,17 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -24762,7 +24766,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>84</v>
@@ -24798,10 +24802,10 @@
         <v>83</v>
       </c>
       <c r="AR164" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AS164" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AT164" t="s" s="2">
         <v>83</v>
@@ -24809,10 +24813,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24835,13 +24839,13 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24880,7 +24884,7 @@
         <v>83</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AC165" s="2"/>
       <c r="AD165" t="s" s="2">
@@ -24890,7 +24894,7 @@
         <v>127</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>84</v>
@@ -24923,13 +24927,13 @@
         <v>83</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR165" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS165" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT165" t="s" s="2">
         <v>83</v>
@@ -24937,10 +24941,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -25067,10 +25071,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -25199,14 +25203,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -25228,10 +25232,10 @@
         <v>121</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>124</v>
@@ -25286,7 +25290,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>84</v>
@@ -25333,10 +25337,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -25362,14 +25366,14 @@
         <v>380</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>83</v>
@@ -25418,7 +25422,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>84</v>
@@ -25442,7 +25446,7 @@
         <v>83</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>83</v>
@@ -25454,7 +25458,7 @@
         <v>83</v>
       </c>
       <c r="AR169" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS169" t="s" s="2">
         <v>83</v>
@@ -25465,10 +25469,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -25494,10 +25498,10 @@
         <v>243</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -25528,7 +25532,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -25546,7 +25550,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>100</v>
@@ -25570,7 +25574,7 @@
         <v>83</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
@@ -25582,10 +25586,10 @@
         <v>83</v>
       </c>
       <c r="AR170" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS170" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT170" t="s" s="2">
         <v>83</v>
@@ -25593,10 +25597,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25622,14 +25626,14 @@
         <v>263</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -25678,7 +25682,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>84</v>
@@ -25714,10 +25718,10 @@
         <v>83</v>
       </c>
       <c r="AR171" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS171" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT171" t="s" s="2">
         <v>83</v>
@@ -25725,10 +25729,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -25754,10 +25758,10 @@
         <v>494</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -25808,7 +25812,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -25844,7 +25848,7 @@
         <v>83</v>
       </c>
       <c r="AR172" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS172" t="s" s="2">
         <v>83</v>
@@ -25855,13 +25859,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>83</v>
@@ -25883,13 +25887,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -25940,7 +25944,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>84</v>
@@ -25964,7 +25968,7 @@
         <v>83</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -25973,13 +25977,13 @@
         <v>83</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR173" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS173" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT173" t="s" s="2">
         <v>83</v>
@@ -25987,10 +25991,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -26117,10 +26121,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -26245,13 +26249,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>83</v>
@@ -26273,13 +26277,13 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -26377,10 +26381,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -26507,10 +26511,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26601,7 +26605,7 @@
         <v>85</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>129</v>
@@ -26628,7 +26632,7 @@
         <v>83</v>
       </c>
       <c r="AR178" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS178" t="s" s="2">
         <v>83</v>
@@ -26639,13 +26643,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="B179" t="s" s="2">
-        <v>781</v>
-      </c>
       <c r="C179" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>83</v>
@@ -26733,7 +26737,7 @@
         <v>85</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>129</v>
@@ -26748,7 +26752,7 @@
         <v>83</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -26771,10 +26775,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -26901,10 +26905,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26993,7 +26997,7 @@
         <v>85</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>129</v>
@@ -27031,10 +27035,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -27074,7 +27078,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>83</v>
@@ -27163,10 +27167,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -27226,7 +27230,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -27253,7 +27257,7 @@
         <v>100</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>112</v>
@@ -27291,13 +27295,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>83</v>
@@ -27385,7 +27389,7 @@
         <v>85</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>129</v>
@@ -27400,7 +27404,7 @@
         <v>83</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
@@ -27423,10 +27427,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27553,10 +27557,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -27645,7 +27649,7 @@
         <v>85</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>129</v>
@@ -27683,10 +27687,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27726,7 +27730,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>83</v>
@@ -27815,10 +27819,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27878,7 +27882,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>83</v>
@@ -27905,7 +27909,7 @@
         <v>100</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>112</v>
@@ -27943,13 +27947,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>83</v>
@@ -28037,7 +28041,7 @@
         <v>85</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>129</v>
@@ -28052,7 +28056,7 @@
         <v>83</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>83</v>
@@ -28075,10 +28079,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -28205,10 +28209,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -28297,7 +28301,7 @@
         <v>85</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>129</v>
@@ -28335,10 +28339,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -28378,7 +28382,7 @@
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S192" t="s" s="2">
         <v>83</v>
@@ -28467,10 +28471,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -28530,7 +28534,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -28557,7 +28561,7 @@
         <v>100</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>112</v>
@@ -28595,10 +28599,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -28638,7 +28642,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>83</v>
@@ -28727,10 +28731,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28819,7 +28823,7 @@
         <v>100</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>112</v>
@@ -28857,14 +28861,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -28886,10 +28890,10 @@
         <v>121</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N196" t="s" s="2">
         <v>124</v>
@@ -28944,7 +28948,7 @@
         <v>83</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>84</v>
@@ -28991,10 +28995,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -29020,14 +29024,14 @@
         <v>380</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>83</v>
@@ -29076,7 +29080,7 @@
         <v>83</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>84</v>
@@ -29112,7 +29116,7 @@
         <v>83</v>
       </c>
       <c r="AR197" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS197" t="s" s="2">
         <v>83</v>
@@ -29123,10 +29127,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -29152,10 +29156,10 @@
         <v>243</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -29186,7 +29190,7 @@
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>83</v>
@@ -29204,7 +29208,7 @@
         <v>83</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>100</v>
@@ -29240,10 +29244,10 @@
         <v>83</v>
       </c>
       <c r="AR198" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS198" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT198" t="s" s="2">
         <v>83</v>
@@ -29251,10 +29255,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -29381,10 +29385,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -29475,7 +29479,7 @@
         <v>85</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>129</v>
@@ -29502,7 +29506,7 @@
         <v>83</v>
       </c>
       <c r="AR200" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS200" t="s" s="2">
         <v>83</v>
@@ -29513,10 +29517,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -29588,14 +29592,14 @@
         <v>83</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AF201" t="s" s="2">
         <v>416</v>
@@ -29607,7 +29611,7 @@
         <v>85</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>112</v>
@@ -29645,13 +29649,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>83</v>
@@ -29714,7 +29718,7 @@
       </c>
       <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>83</v>
@@ -29741,7 +29745,7 @@
         <v>85</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>112</v>
@@ -29779,13 +29783,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>83</v>
@@ -29848,7 +29852,7 @@
       </c>
       <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>83</v>
@@ -29875,7 +29879,7 @@
         <v>85</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>112</v>
@@ -29913,10 +29917,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -30009,7 +30013,7 @@
         <v>100</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>112</v>
@@ -30047,10 +30051,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -30076,14 +30080,14 @@
         <v>263</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>83</v>
@@ -30132,7 +30136,7 @@
         <v>83</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>84</v>
@@ -30168,10 +30172,10 @@
         <v>83</v>
       </c>
       <c r="AR205" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS205" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT205" t="s" s="2">
         <v>83</v>
@@ -30179,10 +30183,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -30309,10 +30313,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -30403,7 +30407,7 @@
         <v>85</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ207" t="s" s="2">
         <v>129</v>
@@ -30430,7 +30434,7 @@
         <v>83</v>
       </c>
       <c r="AR207" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS207" t="s" s="2">
         <v>83</v>
@@ -30441,10 +30445,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -30470,7 +30474,7 @@
         <v>270</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M208" t="s" s="2">
         <v>272</v>
@@ -30550,7 +30554,7 @@
         <v>83</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>83</v>
@@ -30573,10 +30577,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -30602,7 +30606,7 @@
         <v>270</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>282</v>
@@ -30684,7 +30688,7 @@
         <v>83</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>83</v>
@@ -30707,10 +30711,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -30733,13 +30737,13 @@
         <v>83</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -30790,7 +30794,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>84</v>
@@ -30814,7 +30818,7 @@
         <v>83</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>83</v>
@@ -30826,7 +30830,7 @@
         <v>83</v>
       </c>
       <c r="AR210" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS210" t="s" s="2">
         <v>83</v>
@@ -30837,13 +30841,13 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>83</v>
@@ -30865,13 +30869,13 @@
         <v>83</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -30922,7 +30926,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>84</v>
@@ -30955,13 +30959,13 @@
         <v>83</v>
       </c>
       <c r="AQ211" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR211" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS211" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT211" t="s" s="2">
         <v>83</v>
@@ -30969,10 +30973,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -31099,10 +31103,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -31231,14 +31235,14 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
@@ -31260,10 +31264,10 @@
         <v>121</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N214" t="s" s="2">
         <v>124</v>
@@ -31318,7 +31322,7 @@
         <v>83</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>84</v>
@@ -31365,10 +31369,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -31394,14 +31398,14 @@
         <v>380</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>83</v>
@@ -31450,7 +31454,7 @@
         <v>83</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>84</v>
@@ -31486,7 +31490,7 @@
         <v>83</v>
       </c>
       <c r="AR215" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS215" t="s" s="2">
         <v>83</v>
@@ -31497,10 +31501,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -31526,10 +31530,10 @@
         <v>243</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -31560,7 +31564,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>83</v>
@@ -31578,7 +31582,7 @@
         <v>83</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>100</v>
@@ -31614,10 +31618,10 @@
         <v>83</v>
       </c>
       <c r="AR216" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS216" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT216" t="s" s="2">
         <v>83</v>
@@ -31625,10 +31629,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -31755,10 +31759,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -31849,7 +31853,7 @@
         <v>85</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>129</v>
@@ -31876,7 +31880,7 @@
         <v>83</v>
       </c>
       <c r="AR218" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS218" t="s" s="2">
         <v>83</v>
@@ -31887,10 +31891,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -31962,14 +31966,14 @@
         <v>83</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AC219" s="2"/>
       <c r="AD219" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AF219" t="s" s="2">
         <v>416</v>
@@ -31981,7 +31985,7 @@
         <v>85</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ219" t="s" s="2">
         <v>112</v>
@@ -32019,13 +32023,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>83</v>
@@ -32050,7 +32054,7 @@
         <v>163</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M220" t="s" s="2">
         <v>413</v>
@@ -32088,7 +32092,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>83</v>
@@ -32115,7 +32119,7 @@
         <v>85</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ220" t="s" s="2">
         <v>112</v>
@@ -32124,7 +32128,7 @@
         <v>83</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>83</v>
@@ -32153,10 +32157,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>355</v>
@@ -32184,7 +32188,7 @@
         <v>163</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M221" t="s" s="2">
         <v>413</v>
@@ -32249,7 +32253,7 @@
         <v>85</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>112</v>
@@ -32287,10 +32291,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -32383,7 +32387,7 @@
         <v>100</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>112</v>
@@ -32421,10 +32425,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -32450,14 +32454,14 @@
         <v>263</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -32506,7 +32510,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>84</v>
@@ -32542,10 +32546,10 @@
         <v>83</v>
       </c>
       <c r="AR223" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS223" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT223" t="s" s="2">
         <v>83</v>
@@ -32553,10 +32557,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -32683,10 +32687,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -32777,7 +32781,7 @@
         <v>85</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>129</v>
@@ -32804,7 +32808,7 @@
         <v>83</v>
       </c>
       <c r="AR225" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS225" t="s" s="2">
         <v>83</v>
@@ -32815,10 +32819,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -32844,7 +32848,7 @@
         <v>270</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="M226" t="s" s="2">
         <v>272</v>
@@ -32918,7 +32922,7 @@
         <v>83</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>83</v>
@@ -32947,10 +32951,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -32976,7 +32980,7 @@
         <v>270</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="M227" t="s" s="2">
         <v>282</v>
@@ -33052,7 +33056,7 @@
         <v>83</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>83</v>
@@ -33081,10 +33085,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -33110,10 +33114,10 @@
         <v>494</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -33164,7 +33168,7 @@
         <v>83</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>84</v>
@@ -33200,7 +33204,7 @@
         <v>83</v>
       </c>
       <c r="AR228" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS228" t="s" s="2">
         <v>83</v>
@@ -33211,13 +33215,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>83</v>
@@ -33239,13 +33243,13 @@
         <v>83</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -33296,7 +33300,7 @@
         <v>83</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>84</v>
@@ -33329,13 +33333,13 @@
         <v>83</v>
       </c>
       <c r="AQ229" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR229" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS229" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT229" t="s" s="2">
         <v>83</v>
@@ -33343,10 +33347,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -33473,10 +33477,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -33605,14 +33609,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
@@ -33634,10 +33638,10 @@
         <v>121</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N232" t="s" s="2">
         <v>124</v>
@@ -33692,7 +33696,7 @@
         <v>83</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>84</v>
@@ -33739,10 +33743,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -33768,14 +33772,14 @@
         <v>380</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>83</v>
@@ -33824,7 +33828,7 @@
         <v>83</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>84</v>
@@ -33860,7 +33864,7 @@
         <v>83</v>
       </c>
       <c r="AR233" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS233" t="s" s="2">
         <v>83</v>
@@ -33871,10 +33875,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -33900,10 +33904,10 @@
         <v>243</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -33934,7 +33938,7 @@
       </c>
       <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>83</v>
@@ -33952,7 +33956,7 @@
         <v>83</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>100</v>
@@ -33967,7 +33971,7 @@
         <v>112</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>83</v>
@@ -33988,10 +33992,10 @@
         <v>83</v>
       </c>
       <c r="AR234" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS234" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT234" t="s" s="2">
         <v>83</v>
@@ -33999,10 +34003,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -34129,10 +34133,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -34223,7 +34227,7 @@
         <v>85</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>129</v>
@@ -34250,7 +34254,7 @@
         <v>83</v>
       </c>
       <c r="AR236" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS236" t="s" s="2">
         <v>83</v>
@@ -34261,10 +34265,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -34336,7 +34340,7 @@
         <v>83</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -34355,7 +34359,7 @@
         <v>85</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>112</v>
@@ -34393,13 +34397,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>83</v>
@@ -34424,7 +34428,7 @@
         <v>163</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M238" t="s" s="2">
         <v>413</v>
@@ -34462,7 +34466,7 @@
       </c>
       <c r="Y238" s="2"/>
       <c r="Z238" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>83</v>
@@ -34489,7 +34493,7 @@
         <v>85</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>112</v>
@@ -34527,13 +34531,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>83</v>
@@ -34558,7 +34562,7 @@
         <v>163</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="M239" t="s" s="2">
         <v>413</v>
@@ -34596,7 +34600,7 @@
       </c>
       <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>83</v>
@@ -34623,7 +34627,7 @@
         <v>85</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>112</v>
@@ -34661,10 +34665,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -34757,7 +34761,7 @@
         <v>100</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>112</v>
@@ -34795,10 +34799,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -34824,14 +34828,14 @@
         <v>263</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>83</v>
@@ -34880,7 +34884,7 @@
         <v>83</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>84</v>
@@ -34916,10 +34920,10 @@
         <v>83</v>
       </c>
       <c r="AR241" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS241" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT241" t="s" s="2">
         <v>83</v>
@@ -34927,10 +34931,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -35057,10 +35061,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -35151,7 +35155,7 @@
         <v>85</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>129</v>
@@ -35178,7 +35182,7 @@
         <v>83</v>
       </c>
       <c r="AR243" t="s" s="2">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="AS243" t="s" s="2">
         <v>83</v>
@@ -35189,10 +35193,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -35218,7 +35222,7 @@
         <v>270</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M244" t="s" s="2">
         <v>272</v>
@@ -35289,7 +35293,7 @@
         <v>112</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>83</v>
@@ -35321,10 +35325,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -35350,7 +35354,7 @@
         <v>270</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M245" t="s" s="2">
         <v>282</v>
@@ -35423,7 +35427,7 @@
         <v>112</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>83</v>
@@ -35455,10 +35459,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -35484,10 +35488,10 @@
         <v>494</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -35538,7 +35542,7 @@
         <v>83</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>84</v>
@@ -35574,7 +35578,7 @@
         <v>83</v>
       </c>
       <c r="AR246" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS246" t="s" s="2">
         <v>83</v>
@@ -35585,10 +35589,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -35611,19 +35615,19 @@
         <v>83</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>83</v>
@@ -35652,7 +35656,7 @@
       </c>
       <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>83</v>
@@ -35670,7 +35674,7 @@
         <v>83</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>84</v>
@@ -35703,10 +35707,10 @@
         <v>83</v>
       </c>
       <c r="AQ247" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AR247" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AS247" t="s" s="2">
         <v>83</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="916">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1266,7 +1266,7 @@
   </si>
   <si>
     <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1592,10 +1592,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -18358,7 +18354,7 @@
         <v>243</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>510</v>
+        <v>402</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>403</v>
@@ -18377,7 +18373,7 @@
         <v>83</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>83</v>
@@ -18395,10 +18391,10 @@
         <v>167</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -18463,7 +18459,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>467</v>
@@ -18495,7 +18491,7 @@
         <v>468</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>470</v>
@@ -18511,7 +18507,7 @@
         <v>83</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>472</v>
@@ -18597,7 +18593,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>477</v>
@@ -18626,7 +18622,7 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>479</v>
@@ -18729,7 +18725,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>486</v>
@@ -18859,7 +18855,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>493</v>
@@ -18991,13 +18987,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>379</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>83</v>
@@ -19022,7 +19018,7 @@
         <v>380</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>382</v>
@@ -19125,7 +19121,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>390</v>
@@ -19255,7 +19251,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>391</v>
@@ -19387,7 +19383,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>392</v>
@@ -19521,7 +19517,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>401</v>
@@ -19550,7 +19546,7 @@
         <v>243</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>403</v>
@@ -19569,7 +19565,7 @@
         <v>83</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>83</v>
@@ -19587,10 +19583,10 @@
         <v>167</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
@@ -19655,7 +19651,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>467</v>
@@ -19687,7 +19683,7 @@
         <v>468</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>470</v>
@@ -19703,7 +19699,7 @@
         <v>83</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>472</v>
@@ -19789,7 +19785,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>477</v>
@@ -19921,7 +19917,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>486</v>
@@ -20051,7 +20047,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>493</v>
@@ -20183,13 +20179,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>379</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>83</v>
@@ -20214,7 +20210,7 @@
         <v>380</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>382</v>
@@ -20317,7 +20313,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>390</v>
@@ -20447,7 +20443,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>391</v>
@@ -20579,7 +20575,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>392</v>
@@ -20713,7 +20709,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>401</v>
@@ -20742,7 +20738,7 @@
         <v>243</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>403</v>
@@ -20761,7 +20757,7 @@
         <v>83</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>83</v>
@@ -20779,10 +20775,10 @@
         <v>167</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>83</v>
@@ -20847,7 +20843,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>467</v>
@@ -20879,7 +20875,7 @@
         <v>468</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>470</v>
@@ -20895,7 +20891,7 @@
         <v>83</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>472</v>
@@ -20981,7 +20977,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>477</v>
@@ -21113,7 +21109,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>486</v>
@@ -21243,7 +21239,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>493</v>
@@ -21375,10 +21371,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -21404,23 +21400,23 @@
         <v>311</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="O139" t="s" s="2">
+      <c r="P139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q139" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="P139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q139" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="R139" t="s" s="2">
         <v>83</v>
       </c>
@@ -21464,7 +21460,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -21500,21 +21496,21 @@
         <v>83</v>
       </c>
       <c r="AR139" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AS139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT139" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AS139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT139" t="s" s="2">
-        <v>555</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21537,19 +21533,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -21598,7 +21594,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>84</v>
@@ -21631,13 +21627,13 @@
         <v>83</v>
       </c>
       <c r="AQ140" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AR140" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AR140" t="s" s="2">
+      <c r="AS140" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AS140" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AT140" t="s" s="2">
         <v>83</v>
@@ -21645,10 +21641,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21775,10 +21771,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21907,13 +21903,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C143" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>83</v>
@@ -21935,13 +21931,13 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="M143" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -22039,10 +22035,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -22068,16 +22064,16 @@
         <v>185</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
@@ -22106,25 +22102,25 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF144" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>84</v>
@@ -22157,13 +22153,13 @@
         <v>83</v>
       </c>
       <c r="AQ144" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AR144" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AR144" t="s" s="2">
+      <c r="AS144" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AS144" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AT144" t="s" s="2">
         <v>83</v>
@@ -22171,10 +22167,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -22200,16 +22196,16 @@
         <v>114</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>83</v>
@@ -22258,7 +22254,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>84</v>
@@ -22291,10 +22287,10 @@
         <v>83</v>
       </c>
       <c r="AQ145" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AR145" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AR145" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AS145" t="s" s="2">
         <v>83</v>
@@ -22305,14 +22301,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -22334,13 +22330,13 @@
         <v>114</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -22390,7 +22386,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -22408,28 +22404,28 @@
         <v>83</v>
       </c>
       <c r="AL146" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AM146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ146" t="s" s="2">
+      <c r="AR146" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AR146" t="s" s="2">
+      <c r="AS146" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AS146" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AT146" t="s" s="2">
         <v>83</v>
@@ -22437,14 +22433,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -22466,13 +22462,13 @@
         <v>114</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -22522,7 +22518,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>84</v>
@@ -22540,28 +22536,28 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ147" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AM147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP147" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ147" t="s" s="2">
+      <c r="AR147" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AR147" t="s" s="2">
+      <c r="AS147" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AS147" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AT147" t="s" s="2">
         <v>83</v>
@@ -22569,10 +22565,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22598,10 +22594,10 @@
         <v>114</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -22631,28 +22627,28 @@
         <v>167</v>
       </c>
       <c r="Y148" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="Z148" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="Z148" t="s" s="2">
+      <c r="AA148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>84</v>
@@ -22685,13 +22681,13 @@
         <v>83</v>
       </c>
       <c r="AQ148" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AR148" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="AR148" t="s" s="2">
+      <c r="AS148" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="AS148" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="AT148" t="s" s="2">
         <v>83</v>
@@ -22699,10 +22695,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22728,10 +22724,10 @@
         <v>114</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22761,28 +22757,28 @@
         <v>167</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="Z149" t="s" s="2">
+      <c r="AA149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF149" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -22800,25 +22796,25 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP149" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ149" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AM149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ149" t="s" s="2">
+      <c r="AR149" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AR149" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AS149" t="s" s="2">
         <v>83</v>
@@ -22829,10 +22825,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22858,14 +22854,14 @@
         <v>263</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -22914,7 +22910,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>84</v>
@@ -22947,10 +22943,10 @@
         <v>83</v>
       </c>
       <c r="AQ150" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AR150" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AR150" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AS150" t="s" s="2">
         <v>492</v>
@@ -22961,10 +22957,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22987,19 +22983,19 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -23036,7 +23032,7 @@
         <v>83</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -23046,7 +23042,7 @@
         <v>127</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>84</v>
@@ -23058,34 +23054,34 @@
         <v>218</v>
       </c>
       <c r="AJ151" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO151" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AK151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO151" t="s" s="2">
+      <c r="AP151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ151" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AP151" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ151" t="s" s="2">
+      <c r="AR151" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AR151" t="s" s="2">
+      <c r="AS151" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AS151" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AT151" t="s" s="2">
         <v>83</v>
@@ -23093,10 +23089,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -23223,10 +23219,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -23355,13 +23351,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C154" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>83</v>
@@ -23383,13 +23379,13 @@
         <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -23487,10 +23483,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23516,10 +23512,10 @@
         <v>185</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -23549,28 +23545,28 @@
         <v>246</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="Z155" t="s" s="2">
+      <c r="AA155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF155" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -23579,7 +23575,7 @@
         <v>100</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>112</v>
@@ -23603,13 +23599,13 @@
         <v>83</v>
       </c>
       <c r="AQ155" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AR155" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="AR155" t="s" s="2">
+      <c r="AS155" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="AS155" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="AT155" t="s" s="2">
         <v>83</v>
@@ -23617,10 +23613,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -23646,16 +23642,16 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
@@ -23704,7 +23700,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -23737,10 +23733,10 @@
         <v>83</v>
       </c>
       <c r="AQ156" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AR156" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AR156" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="AS156" t="s" s="2">
         <v>485</v>
@@ -23751,10 +23747,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23780,16 +23776,16 @@
         <v>185</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -23817,28 +23813,28 @@
         <v>246</v>
       </c>
       <c r="Y157" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="Z157" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="Z157" t="s" s="2">
+      <c r="AA157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF157" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>84</v>
@@ -23871,13 +23867,13 @@
         <v>83</v>
       </c>
       <c r="AQ157" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AR157" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AS157" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="AR157" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AS157" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="AT157" t="s" s="2">
         <v>83</v>
@@ -23885,10 +23881,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23911,16 +23907,16 @@
         <v>101</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -23970,7 +23966,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -24017,10 +24013,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -24046,10 +24042,10 @@
         <v>263</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -24100,7 +24096,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>84</v>
@@ -24136,7 +24132,7 @@
         <v>208</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AS159" t="s" s="2">
         <v>492</v>
@@ -24147,13 +24143,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C160" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>83</v>
@@ -24175,19 +24171,19 @@
         <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="L160" t="s" s="2">
-        <v>695</v>
-      </c>
       <c r="M160" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -24236,7 +24232,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>84</v>
@@ -24248,13 +24244,13 @@
         <v>218</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>83</v>
@@ -24269,13 +24265,13 @@
         <v>83</v>
       </c>
       <c r="AQ160" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AR160" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AR160" t="s" s="2">
+      <c r="AS160" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AS160" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AT160" t="s" s="2">
         <v>83</v>
@@ -24283,10 +24279,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -24309,19 +24305,19 @@
         <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -24370,7 +24366,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>84</v>
@@ -24397,19 +24393,19 @@
         <v>83</v>
       </c>
       <c r="AO161" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AP161" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ161" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="AP161" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ161" t="s" s="2">
+      <c r="AR161" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AR161" t="s" s="2">
+      <c r="AS161" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="AS161" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="AT161" t="s" s="2">
         <v>83</v>
@@ -24417,10 +24413,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24446,14 +24442,14 @@
         <v>185</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -24481,11 +24477,11 @@
         <v>246</v>
       </c>
       <c r="Y162" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="Z162" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="Z162" t="s" s="2">
-        <v>712</v>
-      </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
       </c>
@@ -24502,7 +24498,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>84</v>
@@ -24535,13 +24531,13 @@
         <v>83</v>
       </c>
       <c r="AQ162" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AR162" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="AR162" t="s" s="2">
+      <c r="AS162" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="AS162" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="AT162" t="s" s="2">
         <v>83</v>
@@ -24549,10 +24545,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -24575,17 +24571,17 @@
         <v>101</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -24634,7 +24630,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>84</v>
@@ -24667,13 +24663,13 @@
         <v>83</v>
       </c>
       <c r="AQ163" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AR163" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="AR163" t="s" s="2">
+      <c r="AS163" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="AS163" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="AT163" t="s" s="2">
         <v>83</v>
@@ -24681,10 +24677,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24707,17 +24703,17 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -24766,7 +24762,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>84</v>
@@ -24802,10 +24798,10 @@
         <v>83</v>
       </c>
       <c r="AR164" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AS164" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AS164" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="AT164" t="s" s="2">
         <v>83</v>
@@ -24813,10 +24809,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24839,13 +24835,13 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="M165" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24884,7 +24880,7 @@
         <v>83</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AC165" s="2"/>
       <c r="AD165" t="s" s="2">
@@ -24894,7 +24890,7 @@
         <v>127</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>84</v>
@@ -24927,13 +24923,13 @@
         <v>83</v>
       </c>
       <c r="AQ165" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR165" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR165" t="s" s="2">
+      <c r="AS165" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS165" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT165" t="s" s="2">
         <v>83</v>
@@ -24941,10 +24937,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -25071,10 +25067,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -25203,14 +25199,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -25232,10 +25228,10 @@
         <v>121</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>124</v>
@@ -25290,7 +25286,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>84</v>
@@ -25337,10 +25333,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -25366,14 +25362,14 @@
         <v>380</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>83</v>
@@ -25422,7 +25418,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>84</v>
@@ -25446,19 +25442,19 @@
         <v>83</v>
       </c>
       <c r="AN169" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR169" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR169" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="AS169" t="s" s="2">
         <v>83</v>
@@ -25469,10 +25465,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -25498,10 +25494,10 @@
         <v>243</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -25532,7 +25528,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -25550,7 +25546,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>100</v>
@@ -25574,22 +25570,22 @@
         <v>83</v>
       </c>
       <c r="AN170" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR170" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AS170" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP170" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ170" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR170" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AS170" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="AT170" t="s" s="2">
         <v>83</v>
@@ -25597,10 +25593,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25626,14 +25622,14 @@
         <v>263</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -25682,7 +25678,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>84</v>
@@ -25718,10 +25714,10 @@
         <v>83</v>
       </c>
       <c r="AR171" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS171" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS171" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT171" t="s" s="2">
         <v>83</v>
@@ -25729,10 +25725,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -25758,10 +25754,10 @@
         <v>494</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -25812,7 +25808,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -25848,7 +25844,7 @@
         <v>83</v>
       </c>
       <c r="AR172" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS172" t="s" s="2">
         <v>83</v>
@@ -25859,13 +25855,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C173" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>83</v>
@@ -25887,13 +25883,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -25944,7 +25940,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>84</v>
@@ -25968,7 +25964,7 @@
         <v>83</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -25977,13 +25973,13 @@
         <v>83</v>
       </c>
       <c r="AQ173" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR173" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR173" t="s" s="2">
+      <c r="AS173" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS173" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT173" t="s" s="2">
         <v>83</v>
@@ -25991,10 +25987,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -26121,10 +26117,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -26249,13 +26245,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>83</v>
@@ -26277,13 +26273,13 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -26381,10 +26377,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -26511,10 +26507,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26643,13 +26639,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C179" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>83</v>
@@ -26752,7 +26748,7 @@
         <v>83</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -26775,10 +26771,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -26905,10 +26901,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B181" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -27035,10 +27031,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B182" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>791</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -27078,7 +27074,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>83</v>
@@ -27167,10 +27163,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -27230,7 +27226,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -27295,13 +27291,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C184" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C184" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>83</v>
@@ -27404,7 +27400,7 @@
         <v>83</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
@@ -27427,10 +27423,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27557,10 +27553,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -27687,10 +27683,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27730,7 +27726,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>83</v>
@@ -27819,10 +27815,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27882,7 +27878,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>83</v>
@@ -27947,13 +27943,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C189" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>83</v>
@@ -28056,7 +28052,7 @@
         <v>83</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>83</v>
@@ -28079,10 +28075,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -28209,10 +28205,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -28339,10 +28335,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -28382,7 +28378,7 @@
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="S192" t="s" s="2">
         <v>83</v>
@@ -28471,10 +28467,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -28534,7 +28530,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -28599,10 +28595,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -28642,7 +28638,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>83</v>
@@ -28731,10 +28727,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28861,14 +28857,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -28890,10 +28886,10 @@
         <v>121</v>
       </c>
       <c r="L196" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M196" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N196" t="s" s="2">
         <v>124</v>
@@ -28948,7 +28944,7 @@
         <v>83</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>84</v>
@@ -28995,10 +28991,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -29024,14 +29020,14 @@
         <v>380</v>
       </c>
       <c r="L197" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M197" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>83</v>
@@ -29080,7 +29076,7 @@
         <v>83</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>84</v>
@@ -29116,7 +29112,7 @@
         <v>83</v>
       </c>
       <c r="AR197" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AS197" t="s" s="2">
         <v>83</v>
@@ -29127,10 +29123,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -29156,10 +29152,10 @@
         <v>243</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M198" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -29190,7 +29186,7 @@
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>83</v>
@@ -29208,7 +29204,7 @@
         <v>83</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>100</v>
@@ -29244,10 +29240,10 @@
         <v>83</v>
       </c>
       <c r="AR198" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AS198" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AT198" t="s" s="2">
         <v>83</v>
@@ -29255,10 +29251,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>820</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -29385,10 +29381,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -29517,10 +29513,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B201" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -29592,14 +29588,14 @@
         <v>83</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AF201" t="s" s="2">
         <v>416</v>
@@ -29649,13 +29645,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>83</v>
@@ -29718,7 +29714,7 @@
       </c>
       <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>83</v>
@@ -29783,13 +29779,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>83</v>
@@ -29852,7 +29848,7 @@
       </c>
       <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>83</v>
@@ -29917,10 +29913,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="B204" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -30051,10 +30047,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -30080,14 +30076,14 @@
         <v>263</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>83</v>
@@ -30136,7 +30132,7 @@
         <v>83</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>84</v>
@@ -30172,10 +30168,10 @@
         <v>83</v>
       </c>
       <c r="AR205" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS205" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS205" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT205" t="s" s="2">
         <v>83</v>
@@ -30183,10 +30179,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="B206" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -30313,10 +30309,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="B207" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -30445,10 +30441,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B208" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="B208" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -30474,7 +30470,7 @@
         <v>270</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M208" t="s" s="2">
         <v>272</v>
@@ -30554,7 +30550,7 @@
         <v>83</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>83</v>
@@ -30577,10 +30573,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="B209" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -30606,7 +30602,7 @@
         <v>270</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>282</v>
@@ -30688,7 +30684,7 @@
         <v>83</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>83</v>
@@ -30711,10 +30707,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -30737,13 +30733,13 @@
         <v>83</v>
       </c>
       <c r="K210" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="L210" t="s" s="2">
         <v>848</v>
       </c>
-      <c r="L210" t="s" s="2">
-        <v>849</v>
-      </c>
       <c r="M210" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -30794,7 +30790,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>84</v>
@@ -30818,7 +30814,7 @@
         <v>83</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>83</v>
@@ -30830,7 +30826,7 @@
         <v>83</v>
       </c>
       <c r="AR210" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS210" t="s" s="2">
         <v>83</v>
@@ -30841,13 +30837,13 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C211" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>83</v>
@@ -30869,13 +30865,13 @@
         <v>83</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -30926,7 +30922,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>84</v>
@@ -30959,13 +30955,13 @@
         <v>83</v>
       </c>
       <c r="AQ211" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR211" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR211" t="s" s="2">
+      <c r="AS211" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS211" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT211" t="s" s="2">
         <v>83</v>
@@ -30973,10 +30969,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -31103,10 +31099,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -31235,14 +31231,14 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
@@ -31264,10 +31260,10 @@
         <v>121</v>
       </c>
       <c r="L214" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M214" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M214" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N214" t="s" s="2">
         <v>124</v>
@@ -31322,7 +31318,7 @@
         <v>83</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>84</v>
@@ -31369,10 +31365,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -31398,14 +31394,14 @@
         <v>380</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M215" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>83</v>
@@ -31454,7 +31450,7 @@
         <v>83</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>84</v>
@@ -31490,7 +31486,7 @@
         <v>83</v>
       </c>
       <c r="AR215" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AS215" t="s" s="2">
         <v>83</v>
@@ -31501,10 +31497,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -31530,10 +31526,10 @@
         <v>243</v>
       </c>
       <c r="L216" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M216" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -31564,7 +31560,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>83</v>
@@ -31582,7 +31578,7 @@
         <v>83</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>100</v>
@@ -31618,10 +31614,10 @@
         <v>83</v>
       </c>
       <c r="AR216" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AS216" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AT216" t="s" s="2">
         <v>83</v>
@@ -31629,10 +31625,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -31759,10 +31755,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -31891,10 +31887,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -31966,14 +31962,14 @@
         <v>83</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC219" s="2"/>
       <c r="AD219" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AF219" t="s" s="2">
         <v>416</v>
@@ -32023,13 +32019,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C220" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>83</v>
@@ -32054,7 +32050,7 @@
         <v>163</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M220" t="s" s="2">
         <v>413</v>
@@ -32092,7 +32088,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>83</v>
@@ -32128,7 +32124,7 @@
         <v>83</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>83</v>
@@ -32157,10 +32153,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>355</v>
@@ -32188,7 +32184,7 @@
         <v>163</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M221" t="s" s="2">
         <v>413</v>
@@ -32291,10 +32287,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -32425,10 +32421,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -32454,14 +32450,14 @@
         <v>263</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -32510,7 +32506,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>84</v>
@@ -32546,10 +32542,10 @@
         <v>83</v>
       </c>
       <c r="AR223" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS223" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS223" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT223" t="s" s="2">
         <v>83</v>
@@ -32557,10 +32553,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -32687,10 +32683,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -32819,10 +32815,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -32848,7 +32844,7 @@
         <v>270</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="M226" t="s" s="2">
         <v>272</v>
@@ -32922,7 +32918,7 @@
         <v>83</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>83</v>
@@ -32951,10 +32947,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -32980,7 +32976,7 @@
         <v>270</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="M227" t="s" s="2">
         <v>282</v>
@@ -33056,7 +33052,7 @@
         <v>83</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>83</v>
@@ -33085,10 +33081,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -33114,10 +33110,10 @@
         <v>494</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M228" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -33168,7 +33164,7 @@
         <v>83</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>84</v>
@@ -33204,7 +33200,7 @@
         <v>83</v>
       </c>
       <c r="AR228" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS228" t="s" s="2">
         <v>83</v>
@@ -33215,13 +33211,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>83</v>
@@ -33243,13 +33239,13 @@
         <v>83</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -33300,7 +33296,7 @@
         <v>83</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>84</v>
@@ -33333,13 +33329,13 @@
         <v>83</v>
       </c>
       <c r="AQ229" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AR229" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="AR229" t="s" s="2">
+      <c r="AS229" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AS229" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AT229" t="s" s="2">
         <v>83</v>
@@ -33347,10 +33343,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -33477,10 +33473,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -33609,14 +33605,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
@@ -33638,10 +33634,10 @@
         <v>121</v>
       </c>
       <c r="L232" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N232" t="s" s="2">
         <v>124</v>
@@ -33696,7 +33692,7 @@
         <v>83</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>84</v>
@@ -33743,10 +33739,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -33772,14 +33768,14 @@
         <v>380</v>
       </c>
       <c r="L233" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>83</v>
@@ -33828,7 +33824,7 @@
         <v>83</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>84</v>
@@ -33864,7 +33860,7 @@
         <v>83</v>
       </c>
       <c r="AR233" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AS233" t="s" s="2">
         <v>83</v>
@@ -33875,10 +33871,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -33904,10 +33900,10 @@
         <v>243</v>
       </c>
       <c r="L234" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -33938,7 +33934,7 @@
       </c>
       <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>83</v>
@@ -33956,7 +33952,7 @@
         <v>83</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>100</v>
@@ -33971,7 +33967,7 @@
         <v>112</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>83</v>
@@ -33992,10 +33988,10 @@
         <v>83</v>
       </c>
       <c r="AR234" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AS234" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AT234" t="s" s="2">
         <v>83</v>
@@ -34003,10 +33999,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -34133,10 +34129,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -34265,10 +34261,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -34340,7 +34336,7 @@
         <v>83</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -34397,13 +34393,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>83</v>
@@ -34428,7 +34424,7 @@
         <v>163</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="M238" t="s" s="2">
         <v>413</v>
@@ -34466,7 +34462,7 @@
       </c>
       <c r="Y238" s="2"/>
       <c r="Z238" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>83</v>
@@ -34531,13 +34527,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>83</v>
@@ -34562,7 +34558,7 @@
         <v>163</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="M239" t="s" s="2">
         <v>413</v>
@@ -34600,7 +34596,7 @@
       </c>
       <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>83</v>
@@ -34665,10 +34661,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -34799,10 +34795,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -34828,14 +34824,14 @@
         <v>263</v>
       </c>
       <c r="L241" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M241" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>83</v>
@@ -34884,7 +34880,7 @@
         <v>83</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>84</v>
@@ -34920,10 +34916,10 @@
         <v>83</v>
       </c>
       <c r="AR241" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AS241" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="AS241" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="AT241" t="s" s="2">
         <v>83</v>
@@ -34931,10 +34927,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -35061,10 +35057,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -35193,10 +35189,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -35222,7 +35218,7 @@
         <v>270</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="M244" t="s" s="2">
         <v>272</v>
@@ -35293,7 +35289,7 @@
         <v>112</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>83</v>
@@ -35325,10 +35321,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -35354,7 +35350,7 @@
         <v>270</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="M245" t="s" s="2">
         <v>282</v>
@@ -35427,7 +35423,7 @@
         <v>112</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>83</v>
@@ -35459,10 +35455,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -35488,10 +35484,10 @@
         <v>494</v>
       </c>
       <c r="L246" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M246" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -35542,7 +35538,7 @@
         <v>83</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>84</v>
@@ -35578,7 +35574,7 @@
         <v>83</v>
       </c>
       <c r="AR246" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AS246" t="s" s="2">
         <v>83</v>
@@ -35589,10 +35585,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -35615,19 +35611,19 @@
         <v>83</v>
       </c>
       <c r="K247" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="L247" t="s" s="2">
         <v>909</v>
       </c>
-      <c r="L247" t="s" s="2">
+      <c r="M247" t="s" s="2">
         <v>910</v>
       </c>
-      <c r="M247" t="s" s="2">
+      <c r="N247" t="s" s="2">
         <v>911</v>
       </c>
-      <c r="N247" t="s" s="2">
+      <c r="O247" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>83</v>
@@ -35656,7 +35652,7 @@
       </c>
       <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>83</v>
@@ -35674,7 +35670,7 @@
         <v>83</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>84</v>
@@ -35707,10 +35703,10 @@
         <v>83</v>
       </c>
       <c r="AQ247" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="AR247" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="AR247" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="AS247" t="s" s="2">
         <v>83</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="920">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>InscriptionOrdre : Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true". Ces données sont uniquement accessibles en accès restreint.</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.id</t>
@@ -734,7 +734,7 @@
     <t>registeringOrganization</t>
   </si>
   <si>
-    <t>ordre</t>
+    <t>InscriptionOrdre.ordre</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.extension:registeringOrganization.id</t>
@@ -876,7 +876,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateDebutInscription</t>
+    <t>InscriptionOrdre.dateDebutInscription</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -906,7 +906,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateRadiation</t>
+    <t>InscriptionOrdre.dateRadiation</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -921,7 +921,7 @@
     <t>status</t>
   </si>
   <si>
-    <t>statutInscription</t>
+    <t>InscriptionOrdre.statutInscription</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.extension:status.id</t>
@@ -945,7 +945,7 @@
     <t>hostingDepartment</t>
   </si>
   <si>
-    <t>conseilDepartemental</t>
+    <t>InscriptionOrdre.conseilDepartemental</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.extension:hostingDepartment.id</t>
@@ -1034,7 +1034,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>typeAutorisation</t>
+    <t>AutorisationExercice.typeAutorisation</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-frpractitioner-authorization.extension:type.id</t>
@@ -1079,7 +1079,7 @@
     <t>dateDebutAutorisation : Date à partir de laquelle l’autorisation s’applique.</t>
   </si>
   <si>
-    <t>dateDebutAutorisation</t>
+    <t>AutorisationExercice.dateDebutAutorisation</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-frpractitioner-authorization.extension:period.value[x].end</t>
@@ -1088,7 +1088,7 @@
     <t>dateFinAutorisation : Date de fin de validité de l'autorisation.</t>
   </si>
   <si>
-    <t>dateFinAutorisation</t>
+    <t>AutorisationExercice.dateFinAutorisation</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-frpractitioner-authorization.extension:field</t>
@@ -1097,7 +1097,7 @@
     <t>field</t>
   </si>
   <si>
-    <t>disciplineAutorisee</t>
+    <t>AutorisationExercice.disciplineAutorisee</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-frpractitioner-authorization.extension:field.id</t>
@@ -1119,6 +1119,9 @@
   </si>
   <si>
     <t>profession</t>
+  </si>
+  <si>
+    <t>AutorisationExercice.profession</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-frpractitioner-authorization.extension:profession.id</t>
@@ -1869,7 +1872,7 @@
     <t>HumanName.family</t>
   </si>
   <si>
-    <t>nomExercice</t>
+    <t>ExerciceProfessionnel.nomExercice</t>
   </si>
   <si>
     <t>XPN.1/FN.1</t>
@@ -1900,7 +1903,7 @@
     <t>HumanName.given</t>
   </si>
   <si>
-    <t>prenomExercice</t>
+    <t>ExerciceProfessionnel.prenomExercice</t>
   </si>
   <si>
     <t>XPN.2 + XPN.3</t>
@@ -1957,7 +1960,7 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>civiliteExercice</t>
+    <t>ExerciceProfessionnel.civiliteExercice</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -2177,7 +2180,7 @@
     <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
   </si>
   <si>
-    <t>boiteLettresMSS</t>
+    <t>ExerciceProfessionnel.boiteLettresMSS</t>
   </si>
   <si>
     <t>Practitioner.address</t>
@@ -2298,7 +2301,7 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:code}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -2346,7 +2349,7 @@
     <t>Often, specific identities are assigned for the qualification.</t>
   </si>
   <si>
-    <t>numeroDiplome</t>
+    <t>Diplome.numeroDiplome</t>
   </si>
   <si>
     <t>.playingEntity.playingRole[classCode=QUAL].id</t>
@@ -2364,7 +2367,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
   </si>
   <si>
-    <t>codeDiplome</t>
+    <t>Diplome.codeDiplome</t>
   </si>
   <si>
     <t>./Qualifications.Value</t>
@@ -2409,7 +2412,7 @@
     <t>Diplôme et type de diplôme, par exemple : DE, DES, CES, etc. (typeDiplome)</t>
   </si>
   <si>
-    <t>typeDiplome</t>
+    <t>Diplome.typeDiplome</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.id</t>
@@ -2452,7 +2455,7 @@
     <t>academicDegree</t>
   </si>
   <si>
-    <t>natureCycleFormation</t>
+    <t>Diplome.natureCycleFormation</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:academicDegree.id</t>
@@ -2488,7 +2491,7 @@
     <t>achievedLevel</t>
   </si>
   <si>
-    <t>anneeUniversitaire</t>
+    <t>Diplome.anneeUniversitaire</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:achievedLevel.id</t>
@@ -2512,7 +2515,7 @@
     <t>academicYear</t>
   </si>
   <si>
-    <t>niveauFormationAcquis</t>
+    <t>Diplome.niveauFormationAcquis</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:academicYear.id</t>
@@ -2570,122 +2573,122 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.coding</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.start</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.start</t>
+  </si>
+  <si>
+    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
+cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
+  </si>
+  <si>
+    <t>Diplome.dateDebut</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.end</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.end</t>
+  </si>
+  <si>
+    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
+  </si>
+  <si>
+    <t>Diplome.dateFin</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.issuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
+  </si>
+  <si>
+    <t>Diplome.lieuFormation</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
-  </si>
-  <si>
-    <t>degreeType</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degree</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.start</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.start</t>
-  </si>
-  <si>
-    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
-cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
-  </si>
-  <si>
-    <t>dateDebut</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.end</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.end</t>
-  </si>
-  <si>
-    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>lieuFormation</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.coding</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
   </si>
   <si>
@@ -2698,12 +2701,18 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
   </si>
   <si>
+    <t>ExerciceProfessionnel.categorieProfession</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
   </si>
   <si>
     <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
   </si>
   <si>
+    <t>ExerciceProfessionnel.profession</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:exercicePro.code.text</t>
   </si>
   <si>
@@ -2722,7 +2731,7 @@
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel exerce cette profession (dateEffetExercice).</t>
   </si>
   <si>
-    <t>dateEffetExercice</t>
+    <t>ExerciceProfessionnel.dateEffetExercice</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.period.end</t>
@@ -2731,7 +2740,7 @@
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
   </si>
   <si>
-    <t>dateFinEffetExercice</t>
+    <t>ExerciceProfessionnel.dateFinEffetExercice</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.issuer</t>
@@ -2743,7 +2752,7 @@
     <t>savoirFaire</t>
   </si>
   <si>
-    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+    <t>savoirFaire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.id</t>
@@ -2761,19 +2770,22 @@
     <t>Practitioner.qualification:savoirFaire.code</t>
   </si>
   <si>
+    <t>SavoirFaire.typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
+  </si>
+  <si>
     <t>typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>Le type de savoir-faire (qualifications/autres attributions).
@@ -2810,7 +2822,7 @@
     <t>Starting time with inclusive boundary</t>
   </si>
   <si>
-    <t>dateReconnaissance</t>
+    <t>SavoirFaire.dateReconnaissance</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.period.end</t>
@@ -2819,7 +2831,7 @@
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>dateAbandon</t>
+    <t>SavoirFaire.dateAbandon</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.issuer</t>
@@ -13954,7 +13966,7 @@
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>83</v>
@@ -13971,7 +13983,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>232</v>
@@ -14101,7 +14113,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>234</v>
@@ -14231,7 +14243,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>236</v>
@@ -14363,7 +14375,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>242</v>
@@ -14426,7 +14438,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -14491,7 +14503,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>313</v>
@@ -14534,7 +14546,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -14623,7 +14635,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>316</v>
@@ -14753,13 +14765,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>209</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>83</v>
@@ -14781,13 +14793,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -14885,13 +14897,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>209</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>83</v>
@@ -14913,13 +14925,13 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -15017,10 +15029,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -15046,16 +15058,16 @@
         <v>121</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>124</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -15104,7 +15116,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>84</v>
@@ -15151,10 +15163,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -15177,17 +15189,17 @@
         <v>101</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -15224,10 +15236,10 @@
         <v>83</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>83</v>
@@ -15236,7 +15248,7 @@
         <v>127</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>84</v>
@@ -15269,24 +15281,24 @@
         <v>83</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AT92" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15413,10 +15425,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15545,10 +15557,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15574,16 +15586,16 @@
         <v>185</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -15611,10 +15623,10 @@
         <v>246</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -15632,7 +15644,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>84</v>
@@ -15668,7 +15680,7 @@
         <v>208</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>83</v>
@@ -15679,10 +15691,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15708,16 +15720,16 @@
         <v>243</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -15746,7 +15758,7 @@
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -15764,7 +15776,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>84</v>
@@ -15797,10 +15809,10 @@
         <v>83</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>83</v>
@@ -15811,10 +15823,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15941,10 +15953,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -16073,10 +16085,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -16102,16 +16114,16 @@
         <v>163</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -16160,7 +16172,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>84</v>
@@ -16193,10 +16205,10 @@
         <v>83</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>83</v>
@@ -16207,10 +16219,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -16337,10 +16349,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16469,10 +16481,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16498,16 +16510,16 @@
         <v>147</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -16520,7 +16532,7 @@
         <v>83</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>83</v>
@@ -16556,7 +16568,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>84</v>
@@ -16589,10 +16601,10 @@
         <v>83</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>83</v>
@@ -16603,10 +16615,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16632,13 +16644,13 @@
         <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16688,7 +16700,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>84</v>
@@ -16721,10 +16733,10 @@
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>83</v>
@@ -16735,10 +16747,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16764,14 +16776,14 @@
         <v>185</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -16820,7 +16832,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>84</v>
@@ -16853,10 +16865,10 @@
         <v>83</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AS104" t="s" s="2">
         <v>83</v>
@@ -16867,10 +16879,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16896,14 +16908,14 @@
         <v>114</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -16952,7 +16964,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>84</v>
@@ -16985,10 +16997,10 @@
         <v>83</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AS105" t="s" s="2">
         <v>83</v>
@@ -16999,10 +17011,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -17028,16 +17040,16 @@
         <v>311</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -17086,7 +17098,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>84</v>
@@ -17119,10 +17131,10 @@
         <v>83</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AR106" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AS106" t="s" s="2">
         <v>83</v>
@@ -17133,10 +17145,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -17162,16 +17174,16 @@
         <v>114</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -17220,7 +17232,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>84</v>
@@ -17253,10 +17265,10 @@
         <v>83</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AS107" t="s" s="2">
         <v>83</v>
@@ -17267,10 +17279,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -17296,16 +17308,16 @@
         <v>147</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -17318,7 +17330,7 @@
         <v>83</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>83</v>
@@ -17354,7 +17366,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>84</v>
@@ -17387,13 +17399,13 @@
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AS108" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AT108" t="s" s="2">
         <v>83</v>
@@ -17401,10 +17413,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17430,13 +17442,13 @@
         <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -17450,7 +17462,7 @@
         <v>83</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>83</v>
@@ -17486,7 +17498,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>84</v>
@@ -17519,13 +17531,13 @@
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AS109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AT109" t="s" s="2">
         <v>83</v>
@@ -17533,10 +17545,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17562,10 +17574,10 @@
         <v>263</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -17616,7 +17628,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>84</v>
@@ -17649,13 +17661,13 @@
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AS110" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AT110" t="s" s="2">
         <v>83</v>
@@ -17663,10 +17675,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17689,16 +17701,16 @@
         <v>101</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -17748,7 +17760,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>84</v>
@@ -17781,13 +17793,13 @@
         <v>83</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AS111" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AT111" t="s" s="2">
         <v>83</v>
@@ -17795,13 +17807,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>83</v>
@@ -17823,17 +17835,17 @@
         <v>101</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -17882,7 +17894,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>84</v>
@@ -17909,30 +17921,30 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AS112" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AT112" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -18059,10 +18071,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -18191,10 +18203,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -18220,16 +18232,16 @@
         <v>185</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -18257,10 +18269,10 @@
         <v>246</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -18278,7 +18290,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>84</v>
@@ -18314,7 +18326,7 @@
         <v>208</v>
       </c>
       <c r="AR115" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS115" t="s" s="2">
         <v>83</v>
@@ -18325,10 +18337,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18354,16 +18366,16 @@
         <v>243</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -18373,7 +18385,7 @@
         <v>83</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>83</v>
@@ -18391,10 +18403,10 @@
         <v>167</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -18412,7 +18424,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>84</v>
@@ -18445,10 +18457,10 @@
         <v>83</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS116" t="s" s="2">
         <v>83</v>
@@ -18459,10 +18471,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18488,16 +18500,16 @@
         <v>147</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -18507,10 +18519,10 @@
         <v>83</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="T117" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="U117" t="s" s="2">
         <v>83</v>
@@ -18546,7 +18558,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>84</v>
@@ -18579,13 +18591,13 @@
         <v>83</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AS117" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AT117" t="s" s="2">
         <v>83</v>
@@ -18593,10 +18605,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18622,13 +18634,13 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -18642,7 +18654,7 @@
         <v>83</v>
       </c>
       <c r="T118" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="U118" t="s" s="2">
         <v>83</v>
@@ -18678,7 +18690,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>84</v>
@@ -18711,13 +18723,13 @@
         <v>83</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AS118" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AT118" t="s" s="2">
         <v>83</v>
@@ -18725,10 +18737,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18754,10 +18766,10 @@
         <v>263</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -18808,7 +18820,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>84</v>
@@ -18841,13 +18853,13 @@
         <v>83</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AS119" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AT119" t="s" s="2">
         <v>83</v>
@@ -18855,10 +18867,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18881,16 +18893,16 @@
         <v>101</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -18940,7 +18952,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>84</v>
@@ -18973,13 +18985,13 @@
         <v>83</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AR120" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AS120" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AT120" t="s" s="2">
         <v>83</v>
@@ -18987,13 +18999,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>83</v>
@@ -19015,17 +19027,17 @@
         <v>101</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -19074,7 +19086,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>84</v>
@@ -19107,24 +19119,24 @@
         <v>83</v>
       </c>
       <c r="AQ121" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AS121" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AT121" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -19251,10 +19263,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -19383,10 +19395,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -19412,16 +19424,16 @@
         <v>185</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -19449,10 +19461,10 @@
         <v>246</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>83</v>
@@ -19470,7 +19482,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>84</v>
@@ -19506,7 +19518,7 @@
         <v>208</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS124" t="s" s="2">
         <v>83</v>
@@ -19517,10 +19529,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19546,16 +19558,16 @@
         <v>243</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -19565,7 +19577,7 @@
         <v>83</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>83</v>
@@ -19583,10 +19595,10 @@
         <v>167</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>83</v>
@@ -19604,7 +19616,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>84</v>
@@ -19637,10 +19649,10 @@
         <v>83</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS125" t="s" s="2">
         <v>83</v>
@@ -19651,10 +19663,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19680,16 +19692,16 @@
         <v>147</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -19699,10 +19711,10 @@
         <v>83</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="T126" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="U126" t="s" s="2">
         <v>83</v>
@@ -19738,7 +19750,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>84</v>
@@ -19771,13 +19783,13 @@
         <v>83</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AS126" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AT126" t="s" s="2">
         <v>83</v>
@@ -19785,10 +19797,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19814,13 +19826,13 @@
         <v>114</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -19834,7 +19846,7 @@
         <v>83</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>83</v>
@@ -19870,7 +19882,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>84</v>
@@ -19903,13 +19915,13 @@
         <v>83</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AS127" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AT127" t="s" s="2">
         <v>83</v>
@@ -19917,10 +19929,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19946,10 +19958,10 @@
         <v>263</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -20000,7 +20012,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>84</v>
@@ -20033,13 +20045,13 @@
         <v>83</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AS128" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AT128" t="s" s="2">
         <v>83</v>
@@ -20047,10 +20059,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -20073,16 +20085,16 @@
         <v>101</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -20132,7 +20144,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>84</v>
@@ -20165,13 +20177,13 @@
         <v>83</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AS129" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AT129" t="s" s="2">
         <v>83</v>
@@ -20179,13 +20191,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>83</v>
@@ -20207,17 +20219,17 @@
         <v>101</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -20266,7 +20278,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>84</v>
@@ -20299,24 +20311,24 @@
         <v>83</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AS130" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AT130" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -20443,10 +20455,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -20575,10 +20587,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20604,16 +20616,16 @@
         <v>185</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
@@ -20641,10 +20653,10 @@
         <v>246</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>83</v>
@@ -20662,7 +20674,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>84</v>
@@ -20698,7 +20710,7 @@
         <v>208</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS133" t="s" s="2">
         <v>83</v>
@@ -20709,10 +20721,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20738,16 +20750,16 @@
         <v>243</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>83</v>
@@ -20757,7 +20769,7 @@
         <v>83</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>83</v>
@@ -20775,10 +20787,10 @@
         <v>167</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>83</v>
@@ -20796,7 +20808,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>84</v>
@@ -20829,10 +20841,10 @@
         <v>83</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AS134" t="s" s="2">
         <v>83</v>
@@ -20843,10 +20855,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20872,16 +20884,16 @@
         <v>147</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>83</v>
@@ -20891,10 +20903,10 @@
         <v>83</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T135" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="U135" t="s" s="2">
         <v>83</v>
@@ -20930,7 +20942,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>84</v>
@@ -20963,13 +20975,13 @@
         <v>83</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AS135" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AT135" t="s" s="2">
         <v>83</v>
@@ -20977,10 +20989,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -21006,13 +21018,13 @@
         <v>114</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -21026,7 +21038,7 @@
         <v>83</v>
       </c>
       <c r="T136" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="U136" t="s" s="2">
         <v>83</v>
@@ -21062,7 +21074,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>84</v>
@@ -21095,13 +21107,13 @@
         <v>83</v>
       </c>
       <c r="AQ136" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AR136" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AS136" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AT136" t="s" s="2">
         <v>83</v>
@@ -21109,10 +21121,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -21138,10 +21150,10 @@
         <v>263</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -21192,7 +21204,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>84</v>
@@ -21225,13 +21237,13 @@
         <v>83</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR137" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AS137" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AT137" t="s" s="2">
         <v>83</v>
@@ -21239,10 +21251,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -21265,16 +21277,16 @@
         <v>101</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -21324,7 +21336,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>84</v>
@@ -21357,13 +21369,13 @@
         <v>83</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AR138" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AS138" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AT138" t="s" s="2">
         <v>83</v>
@@ -21371,10 +21383,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -21400,67 +21412,67 @@
         <v>311</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q139" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="R139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF139" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="P139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q139" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="R139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -21496,21 +21508,21 @@
         <v>83</v>
       </c>
       <c r="AR139" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AS139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT139" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21533,19 +21545,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -21594,7 +21606,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>84</v>
@@ -21627,13 +21639,13 @@
         <v>83</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AR140" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AS140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AT140" t="s" s="2">
         <v>83</v>
@@ -21641,10 +21653,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21771,10 +21783,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21903,13 +21915,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="B143" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="C143" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>83</v>
@@ -21931,13 +21943,13 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -22035,10 +22047,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -22064,16 +22076,16 @@
         <v>185</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
@@ -22102,7 +22114,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>83</v>
@@ -22120,7 +22132,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>84</v>
@@ -22153,13 +22165,13 @@
         <v>83</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AS144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AT144" t="s" s="2">
         <v>83</v>
@@ -22167,10 +22179,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -22196,16 +22208,16 @@
         <v>114</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>83</v>
@@ -22254,7 +22266,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>84</v>
@@ -22287,10 +22299,10 @@
         <v>83</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AS145" t="s" s="2">
         <v>83</v>
@@ -22301,14 +22313,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -22330,13 +22342,13 @@
         <v>114</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -22386,7 +22398,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>84</v>
@@ -22404,7 +22416,7 @@
         <v>83</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>83</v>
@@ -22419,13 +22431,13 @@
         <v>83</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AS146" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AT146" t="s" s="2">
         <v>83</v>
@@ -22433,14 +22445,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -22462,13 +22474,13 @@
         <v>114</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -22518,7 +22530,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>84</v>
@@ -22536,7 +22548,7 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>83</v>
@@ -22551,13 +22563,13 @@
         <v>83</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AS147" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AT147" t="s" s="2">
         <v>83</v>
@@ -22565,10 +22577,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22594,10 +22606,10 @@
         <v>114</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -22627,10 +22639,10 @@
         <v>167</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>83</v>
@@ -22648,7 +22660,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>84</v>
@@ -22681,13 +22693,13 @@
         <v>83</v>
       </c>
       <c r="AQ148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AR148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AS148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AT148" t="s" s="2">
         <v>83</v>
@@ -22695,10 +22707,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22724,10 +22736,10 @@
         <v>114</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -22757,10 +22769,10 @@
         <v>167</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>83</v>
@@ -22778,7 +22790,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>84</v>
@@ -22796,7 +22808,7 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>83</v>
@@ -22811,10 +22823,10 @@
         <v>83</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AS149" t="s" s="2">
         <v>83</v>
@@ -22825,10 +22837,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22854,14 +22866,14 @@
         <v>263</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -22910,7 +22922,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>84</v>
@@ -22943,13 +22955,13 @@
         <v>83</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AS150" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AT150" t="s" s="2">
         <v>83</v>
@@ -22957,10 +22969,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22983,19 +22995,19 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -23032,7 +23044,7 @@
         <v>83</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -23042,7 +23054,7 @@
         <v>127</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>84</v>
@@ -23054,7 +23066,7 @@
         <v>218</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>83</v>
@@ -23069,19 +23081,19 @@
         <v>83</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AS151" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AT151" t="s" s="2">
         <v>83</v>
@@ -23089,10 +23101,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -23219,10 +23231,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -23351,13 +23363,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="B154" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="C154" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>83</v>
@@ -23379,13 +23391,13 @@
         <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -23483,10 +23495,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23512,10 +23524,10 @@
         <v>185</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -23545,10 +23557,10 @@
         <v>246</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>83</v>
@@ -23566,7 +23578,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>84</v>
@@ -23575,7 +23587,7 @@
         <v>100</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>112</v>
@@ -23599,13 +23611,13 @@
         <v>83</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AS155" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AT155" t="s" s="2">
         <v>83</v>
@@ -23613,10 +23625,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -23642,16 +23654,16 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
@@ -23700,7 +23712,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>84</v>
@@ -23733,13 +23745,13 @@
         <v>83</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AR156" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AS156" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AT156" t="s" s="2">
         <v>83</v>
@@ -23747,10 +23759,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23776,16 +23788,16 @@
         <v>185</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -23813,10 +23825,10 @@
         <v>246</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>83</v>
@@ -23834,7 +23846,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>84</v>
@@ -23867,13 +23879,13 @@
         <v>83</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AS157" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AT157" t="s" s="2">
         <v>83</v>
@@ -23881,10 +23893,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23907,16 +23919,16 @@
         <v>101</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -23966,7 +23978,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>84</v>
@@ -24013,10 +24025,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -24042,10 +24054,10 @@
         <v>263</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -24096,7 +24108,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>84</v>
@@ -24132,10 +24144,10 @@
         <v>208</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AS159" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AT159" t="s" s="2">
         <v>83</v>
@@ -24143,13 +24155,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>83</v>
@@ -24171,19 +24183,19 @@
         <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -24232,7 +24244,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>84</v>
@@ -24244,13 +24256,13 @@
         <v>218</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>83</v>
@@ -24265,13 +24277,13 @@
         <v>83</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AR160" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AS160" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AT160" t="s" s="2">
         <v>83</v>
@@ -24279,10 +24291,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -24305,19 +24317,19 @@
         <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -24366,7 +24378,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>84</v>
@@ -24393,19 +24405,19 @@
         <v>83</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AP161" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AS161" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AT161" t="s" s="2">
         <v>83</v>
@@ -24413,10 +24425,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24442,14 +24454,14 @@
         <v>185</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -24477,10 +24489,10 @@
         <v>246</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
@@ -24498,7 +24510,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>84</v>
@@ -24531,13 +24543,13 @@
         <v>83</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AS162" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AT162" t="s" s="2">
         <v>83</v>
@@ -24545,10 +24557,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -24571,17 +24583,17 @@
         <v>101</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -24630,7 +24642,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>84</v>
@@ -24663,13 +24675,13 @@
         <v>83</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AR163" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AS163" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AT163" t="s" s="2">
         <v>83</v>
@@ -24677,10 +24689,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -24703,17 +24715,17 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -24762,7 +24774,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>84</v>
@@ -24798,10 +24810,10 @@
         <v>83</v>
       </c>
       <c r="AR164" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AS164" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AT164" t="s" s="2">
         <v>83</v>
@@ -24809,10 +24821,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24835,13 +24847,13 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24880,7 +24892,7 @@
         <v>83</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AC165" s="2"/>
       <c r="AD165" t="s" s="2">
@@ -24890,7 +24902,7 @@
         <v>127</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>84</v>
@@ -24923,13 +24935,13 @@
         <v>83</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR165" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS165" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT165" t="s" s="2">
         <v>83</v>
@@ -24937,10 +24949,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -25067,10 +25079,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -25199,14 +25211,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -25228,16 +25240,16 @@
         <v>121</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>124</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>83</v>
@@ -25286,7 +25298,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>84</v>
@@ -25333,10 +25345,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -25359,17 +25371,17 @@
         <v>83</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>83</v>
@@ -25418,7 +25430,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>84</v>
@@ -25442,7 +25454,7 @@
         <v>83</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>83</v>
@@ -25454,7 +25466,7 @@
         <v>83</v>
       </c>
       <c r="AR169" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS169" t="s" s="2">
         <v>83</v>
@@ -25465,10 +25477,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -25494,10 +25506,10 @@
         <v>243</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -25528,7 +25540,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -25546,7 +25558,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>100</v>
@@ -25570,7 +25582,7 @@
         <v>83</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
@@ -25582,10 +25594,10 @@
         <v>83</v>
       </c>
       <c r="AR170" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS170" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT170" t="s" s="2">
         <v>83</v>
@@ -25593,10 +25605,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25622,14 +25634,14 @@
         <v>263</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -25678,7 +25690,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>84</v>
@@ -25714,10 +25726,10 @@
         <v>83</v>
       </c>
       <c r="AR171" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS171" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT171" t="s" s="2">
         <v>83</v>
@@ -25725,10 +25737,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -25751,13 +25763,13 @@
         <v>83</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -25808,7 +25820,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>84</v>
@@ -25844,7 +25856,7 @@
         <v>83</v>
       </c>
       <c r="AR172" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS172" t="s" s="2">
         <v>83</v>
@@ -25855,13 +25867,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>83</v>
@@ -25883,13 +25895,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -25940,7 +25952,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>84</v>
@@ -25964,7 +25976,7 @@
         <v>83</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -25973,13 +25985,13 @@
         <v>83</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR173" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS173" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT173" t="s" s="2">
         <v>83</v>
@@ -25987,10 +25999,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -26117,10 +26129,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -26245,13 +26257,13 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>83</v>
@@ -26273,13 +26285,13 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -26377,10 +26389,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -26507,10 +26519,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -26639,13 +26651,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="B179" t="s" s="2">
-        <v>781</v>
-      </c>
       <c r="C179" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>83</v>
@@ -26748,7 +26760,7 @@
         <v>83</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -26771,10 +26783,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -26901,10 +26913,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -27031,10 +27043,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -27074,7 +27086,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>83</v>
@@ -27163,10 +27175,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -27226,7 +27238,7 @@
       </c>
       <c r="Y183" s="2"/>
       <c r="Z183" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -27291,13 +27303,13 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D184" t="s" s="2">
         <v>83</v>
@@ -27400,7 +27412,7 @@
         <v>83</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
@@ -27423,10 +27435,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27553,10 +27565,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -27683,10 +27695,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27726,7 +27738,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>83</v>
@@ -27815,10 +27827,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27878,7 +27890,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>83</v>
@@ -27943,13 +27955,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>83</v>
@@ -28052,7 +28064,7 @@
         <v>83</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>83</v>
@@ -28075,10 +28087,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -28205,10 +28217,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -28335,10 +28347,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -28378,7 +28390,7 @@
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="S192" t="s" s="2">
         <v>83</v>
@@ -28467,10 +28479,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -28530,7 +28542,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -28595,10 +28607,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -28638,7 +28650,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>83</v>
@@ -28727,10 +28739,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28857,14 +28869,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -28886,16 +28898,16 @@
         <v>121</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N196" t="s" s="2">
         <v>124</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>83</v>
@@ -28944,7 +28956,7 @@
         <v>83</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>84</v>
@@ -28991,10 +29003,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -29017,17 +29029,17 @@
         <v>83</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>83</v>
@@ -29076,7 +29088,7 @@
         <v>83</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>84</v>
@@ -29112,7 +29124,7 @@
         <v>83</v>
       </c>
       <c r="AR197" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS197" t="s" s="2">
         <v>83</v>
@@ -29123,10 +29135,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -29152,10 +29164,10 @@
         <v>243</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -29186,7 +29198,7 @@
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>83</v>
@@ -29204,7 +29216,7 @@
         <v>83</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>100</v>
@@ -29240,10 +29252,10 @@
         <v>83</v>
       </c>
       <c r="AR198" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS198" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT198" t="s" s="2">
         <v>83</v>
@@ -29251,10 +29263,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -29381,10 +29393,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -29513,10 +29525,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -29542,16 +29554,16 @@
         <v>163</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>83</v>
@@ -29588,7 +29600,7 @@
         <v>83</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>824</v>
+        <v>735</v>
       </c>
       <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
@@ -29598,7 +29610,7 @@
         <v>825</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>84</v>
@@ -29631,10 +29643,10 @@
         <v>83</v>
       </c>
       <c r="AQ201" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR201" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS201" t="s" s="2">
         <v>83</v>
@@ -29648,7 +29660,7 @@
         <v>826</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C202" t="s" s="2">
         <v>827</v>
@@ -29676,16 +29688,16 @@
         <v>163</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>83</v>
@@ -29732,7 +29744,7 @@
         <v>83</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>84</v>
@@ -29765,10 +29777,10 @@
         <v>83</v>
       </c>
       <c r="AQ202" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR202" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS202" t="s" s="2">
         <v>83</v>
@@ -29782,10 +29794,10 @@
         <v>829</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>83</v>
@@ -29810,16 +29822,16 @@
         <v>163</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>83</v>
@@ -29848,7 +29860,7 @@
       </c>
       <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>83</v>
@@ -29866,7 +29878,7 @@
         <v>83</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>84</v>
@@ -29899,10 +29911,10 @@
         <v>83</v>
       </c>
       <c r="AQ203" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR203" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS203" t="s" s="2">
         <v>83</v>
@@ -29942,16 +29954,16 @@
         <v>114</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>83</v>
@@ -30000,7 +30012,7 @@
         <v>83</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>84</v>
@@ -30033,10 +30045,10 @@
         <v>83</v>
       </c>
       <c r="AQ204" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR204" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AS204" t="s" s="2">
         <v>83</v>
@@ -30050,7 +30062,7 @@
         <v>832</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -30079,11 +30091,11 @@
         <v>833</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>83</v>
@@ -30132,7 +30144,7 @@
         <v>83</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>84</v>
@@ -30168,10 +30180,10 @@
         <v>83</v>
       </c>
       <c r="AR205" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS205" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT205" t="s" s="2">
         <v>83</v>
@@ -30710,7 +30722,7 @@
         <v>846</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -30739,7 +30751,7 @@
         <v>848</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -30790,7 +30802,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>84</v>
@@ -30826,7 +30838,7 @@
         <v>83</v>
       </c>
       <c r="AR210" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS210" t="s" s="2">
         <v>83</v>
@@ -30840,7 +30852,7 @@
         <v>850</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>851</v>
@@ -30865,13 +30877,13 @@
         <v>83</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L211" t="s" s="2">
         <v>852</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -30922,7 +30934,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>84</v>
@@ -30955,13 +30967,13 @@
         <v>83</v>
       </c>
       <c r="AQ211" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR211" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS211" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT211" t="s" s="2">
         <v>83</v>
@@ -30972,7 +30984,7 @@
         <v>853</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -31102,7 +31114,7 @@
         <v>854</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -31234,11 +31246,11 @@
         <v>855</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
@@ -31260,16 +31272,16 @@
         <v>121</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N214" t="s" s="2">
         <v>124</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>83</v>
@@ -31318,7 +31330,7 @@
         <v>83</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>84</v>
@@ -31368,7 +31380,7 @@
         <v>856</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -31391,17 +31403,17 @@
         <v>83</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>83</v>
@@ -31450,7 +31462,7 @@
         <v>83</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>84</v>
@@ -31486,7 +31498,7 @@
         <v>83</v>
       </c>
       <c r="AR215" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS215" t="s" s="2">
         <v>83</v>
@@ -31500,7 +31512,7 @@
         <v>857</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -31526,10 +31538,10 @@
         <v>243</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -31560,7 +31572,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>83</v>
@@ -31578,7 +31590,7 @@
         <v>83</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>100</v>
@@ -31614,10 +31626,10 @@
         <v>83</v>
       </c>
       <c r="AR216" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS216" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT216" t="s" s="2">
         <v>83</v>
@@ -31628,7 +31640,7 @@
         <v>858</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -31758,7 +31770,7 @@
         <v>859</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -31890,7 +31902,7 @@
         <v>860</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -31916,16 +31928,16 @@
         <v>163</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O219" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>83</v>
@@ -31962,7 +31974,7 @@
         <v>83</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>824</v>
+        <v>861</v>
       </c>
       <c r="AC219" s="2"/>
       <c r="AD219" t="s" s="2">
@@ -31972,7 +31984,7 @@
         <v>825</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>84</v>
@@ -32005,10 +32017,10 @@
         <v>83</v>
       </c>
       <c r="AQ219" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR219" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS219" t="s" s="2">
         <v>83</v>
@@ -32019,13 +32031,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>83</v>
@@ -32050,16 +32062,16 @@
         <v>163</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>83</v>
@@ -32088,7 +32100,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>83</v>
@@ -32106,7 +32118,7 @@
         <v>83</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>84</v>
@@ -32124,7 +32136,7 @@
         <v>83</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>83</v>
@@ -32139,10 +32151,10 @@
         <v>83</v>
       </c>
       <c r="AQ220" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR220" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS220" t="s" s="2">
         <v>83</v>
@@ -32153,10 +32165,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>355</v>
@@ -32184,16 +32196,16 @@
         <v>163</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>83</v>
@@ -32222,7 +32234,7 @@
       </c>
       <c r="Y221" s="2"/>
       <c r="Z221" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>83</v>
@@ -32240,7 +32252,7 @@
         <v>83</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>84</v>
@@ -32258,7 +32270,7 @@
         <v>83</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>355</v>
+        <v>869</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>83</v>
@@ -32273,10 +32285,10 @@
         <v>83</v>
       </c>
       <c r="AQ221" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR221" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS221" t="s" s="2">
         <v>83</v>
@@ -32287,7 +32299,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>831</v>
@@ -32316,16 +32328,16 @@
         <v>114</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O222" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>83</v>
@@ -32374,7 +32386,7 @@
         <v>83</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>84</v>
@@ -32407,10 +32419,10 @@
         <v>83</v>
       </c>
       <c r="AQ222" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR222" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AS222" t="s" s="2">
         <v>83</v>
@@ -32421,10 +32433,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -32450,14 +32462,14 @@
         <v>263</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -32506,7 +32518,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>84</v>
@@ -32542,10 +32554,10 @@
         <v>83</v>
       </c>
       <c r="AR223" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS223" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT223" t="s" s="2">
         <v>83</v>
@@ -32553,7 +32565,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>835</v>
@@ -32683,7 +32695,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>837</v>
@@ -32815,7 +32827,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>839</v>
@@ -32844,7 +32856,7 @@
         <v>270</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="M226" t="s" s="2">
         <v>272</v>
@@ -32918,7 +32930,7 @@
         <v>83</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>83</v>
@@ -32947,7 +32959,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>843</v>
@@ -32976,7 +32988,7 @@
         <v>270</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="M227" t="s" s="2">
         <v>282</v>
@@ -33052,7 +33064,7 @@
         <v>83</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>83</v>
@@ -33081,10 +33093,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -33107,13 +33119,13 @@
         <v>83</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -33164,7 +33176,7 @@
         <v>83</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>84</v>
@@ -33200,7 +33212,7 @@
         <v>83</v>
       </c>
       <c r="AR228" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS228" t="s" s="2">
         <v>83</v>
@@ -33211,13 +33223,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>83</v>
@@ -33239,13 +33251,13 @@
         <v>83</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -33296,7 +33308,7 @@
         <v>83</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>84</v>
@@ -33329,13 +33341,13 @@
         <v>83</v>
       </c>
       <c r="AQ229" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AR229" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS229" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AT229" t="s" s="2">
         <v>83</v>
@@ -33343,10 +33355,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -33473,10 +33485,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -33605,14 +33617,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
@@ -33634,16 +33646,16 @@
         <v>121</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N232" t="s" s="2">
         <v>124</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>83</v>
@@ -33692,7 +33704,7 @@
         <v>83</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>84</v>
@@ -33739,10 +33751,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -33765,17 +33777,17 @@
         <v>83</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>83</v>
@@ -33824,7 +33836,7 @@
         <v>83</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>84</v>
@@ -33860,7 +33872,7 @@
         <v>83</v>
       </c>
       <c r="AR233" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AS233" t="s" s="2">
         <v>83</v>
@@ -33871,10 +33883,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -33900,10 +33912,10 @@
         <v>243</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -33934,7 +33946,7 @@
       </c>
       <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>83</v>
@@ -33952,7 +33964,7 @@
         <v>83</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>100</v>
@@ -33967,7 +33979,7 @@
         <v>112</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>83</v>
@@ -33988,10 +34000,10 @@
         <v>83</v>
       </c>
       <c r="AR234" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AS234" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AT234" t="s" s="2">
         <v>83</v>
@@ -33999,10 +34011,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -34129,10 +34141,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -34261,10 +34273,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -34290,16 +34302,16 @@
         <v>163</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>83</v>
@@ -34336,7 +34348,7 @@
         <v>83</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>824</v>
+        <v>861</v>
       </c>
       <c r="AC237" s="2"/>
       <c r="AD237" t="s" s="2">
@@ -34346,7 +34358,7 @@
         <v>127</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>84</v>
@@ -34379,10 +34391,10 @@
         <v>83</v>
       </c>
       <c r="AQ237" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR237" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS237" t="s" s="2">
         <v>83</v>
@@ -34393,13 +34405,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>83</v>
@@ -34424,16 +34436,16 @@
         <v>163</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>83</v>
@@ -34462,7 +34474,7 @@
       </c>
       <c r="Y238" s="2"/>
       <c r="Z238" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>83</v>
@@ -34480,7 +34492,7 @@
         <v>83</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>84</v>
@@ -34513,10 +34525,10 @@
         <v>83</v>
       </c>
       <c r="AQ238" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR238" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS238" t="s" s="2">
         <v>83</v>
@@ -34527,13 +34539,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>83</v>
@@ -34558,16 +34570,16 @@
         <v>163</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>83</v>
@@ -34596,7 +34608,7 @@
       </c>
       <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>83</v>
@@ -34614,7 +34626,7 @@
         <v>83</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>84</v>
@@ -34647,10 +34659,10 @@
         <v>83</v>
       </c>
       <c r="AQ239" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR239" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS239" t="s" s="2">
         <v>83</v>
@@ -34661,7 +34673,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>831</v>
@@ -34690,16 +34702,16 @@
         <v>114</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O240" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>83</v>
@@ -34748,7 +34760,7 @@
         <v>83</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>84</v>
@@ -34781,10 +34793,10 @@
         <v>83</v>
       </c>
       <c r="AQ240" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR240" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AS240" t="s" s="2">
         <v>83</v>
@@ -34795,10 +34807,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -34824,14 +34836,14 @@
         <v>263</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>83</v>
@@ -34880,7 +34892,7 @@
         <v>83</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>84</v>
@@ -34916,10 +34928,10 @@
         <v>83</v>
       </c>
       <c r="AR241" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AS241" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AT241" t="s" s="2">
         <v>83</v>
@@ -34927,7 +34939,7 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>835</v>
@@ -35057,7 +35069,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>837</v>
@@ -35189,7 +35201,7 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>839</v>
@@ -35218,7 +35230,7 @@
         <v>270</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="M244" t="s" s="2">
         <v>272</v>
@@ -35289,7 +35301,7 @@
         <v>112</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>83</v>
@@ -35321,7 +35333,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>843</v>
@@ -35350,7 +35362,7 @@
         <v>270</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="M245" t="s" s="2">
         <v>282</v>
@@ -35423,7 +35435,7 @@
         <v>112</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>83</v>
@@ -35455,10 +35467,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -35481,13 +35493,13 @@
         <v>83</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N246" s="2"/>
       <c r="O246" s="2"/>
@@ -35538,7 +35550,7 @@
         <v>83</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>84</v>
@@ -35574,7 +35586,7 @@
         <v>83</v>
       </c>
       <c r="AR246" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AS246" t="s" s="2">
         <v>83</v>
@@ -35585,10 +35597,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -35611,19 +35623,19 @@
         <v>83</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>83</v>
@@ -35652,7 +35664,7 @@
       </c>
       <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>83</v>
@@ -35670,7 +35682,7 @@
         <v>83</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>84</v>
@@ -35703,10 +35715,10 @@
         <v>83</v>
       </c>
       <c r="AQ247" t="s" s="2">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="AR247" t="s" s="2">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="AS247" t="s" s="2">
         <v>83</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -25175,7 +25175,7 @@
         <v>85</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>84</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>102</v>
@@ -23959,7 +23959,7 @@
         <v>86</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>84</v>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>102</v>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$301</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12672" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12883" uniqueCount="975">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2636,6 +2636,30 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J88-AnneeUniversitaire-RASS/FHIR/JDV-J88-AnneeUniversitaire-RASS|20251016120000</t>
   </si>
   <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation</t>
+  </si>
+  <si>
+    <t>trainingLocation</t>
+  </si>
+  <si>
+    <t>Diplome.lieuFormation</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.url</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J235-LieuFormation-EPARS/FHIR/JDV-J235-LieuFormation-EPARS|20240726120000</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:degree.extension:as-ext-education-level.url</t>
   </si>
   <si>
@@ -2788,16 +2812,6 @@
   </si>
   <si>
     <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>Diplome.lieuFormation</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro</t>
@@ -3332,7 +3346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AU296"/>
+  <dimension ref="A1:AU301"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="82.7265625" customWidth="true" bestFit="true"/>
@@ -35867,26 +35881,28 @@
         <v>84</v>
       </c>
     </row>
-    <row r="243" hidden="true">
+    <row r="243">
       <c r="A243" t="s" s="2">
         <v>844</v>
       </c>
       <c r="B243" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C243" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G243" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H243" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I243" t="s" s="2">
         <v>84</v>
@@ -35895,91 +35911,89 @@
         <v>84</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N243" s="2"/>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q243" s="2"/>
       <c r="R243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF243" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG243" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH243" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ243" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM243" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN243" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="S243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AO243" t="s" s="2">
         <v>84</v>
       </c>
@@ -35993,7 +36007,7 @@
         <v>84</v>
       </c>
       <c r="AS243" t="s" s="2">
-        <v>205</v>
+        <v>84</v>
       </c>
       <c r="AT243" t="s" s="2">
         <v>84</v>
@@ -36007,7 +36021,7 @@
         <v>847</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>848</v>
+        <v>820</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -36018,7 +36032,7 @@
         <v>85</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>84</v>
@@ -36030,13 +36044,13 @@
         <v>84</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>241</v>
+        <v>117</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>242</v>
+        <v>118</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -36087,7 +36101,7 @@
         <v>84</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>245</v>
+        <v>119</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>85</v>
@@ -36099,7 +36113,7 @@
         <v>84</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>84</v>
@@ -36126,7 +36140,7 @@
         <v>84</v>
       </c>
       <c r="AS244" t="s" s="2">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="AT244" t="s" s="2">
         <v>84</v>
@@ -36137,46 +36151,42 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>774</v>
+        <v>822</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>775</v>
+        <v>84</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I245" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J245" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K245" t="s" s="2">
         <v>123</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>776</v>
+        <v>207</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O245" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
         <v>84</v>
       </c>
@@ -36212,19 +36222,19 @@
         <v>84</v>
       </c>
       <c r="AB245" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC245" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD245" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE245" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>778</v>
+        <v>130</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>85</v>
@@ -36263,7 +36273,7 @@
         <v>84</v>
       </c>
       <c r="AS245" t="s" s="2">
-        <v>205</v>
+        <v>84</v>
       </c>
       <c r="AT245" t="s" s="2">
         <v>84</v>
@@ -36274,10 +36284,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>779</v>
+        <v>824</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -36285,10 +36295,10 @@
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H246" t="s" s="2">
         <v>84</v>
@@ -36300,24 +36310,24 @@
         <v>84</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>780</v>
+        <v>234</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" t="s" s="2">
-        <v>782</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q246" s="2"/>
       <c r="R246" t="s" s="2">
-        <v>84</v>
+        <v>845</v>
       </c>
       <c r="S246" t="s" s="2">
         <v>84</v>
@@ -36359,19 +36369,19 @@
         <v>84</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>779</v>
+        <v>237</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH246" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI246" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ246" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK246" t="s" s="2">
         <v>84</v>
@@ -36398,7 +36408,7 @@
         <v>84</v>
       </c>
       <c r="AS246" t="s" s="2">
-        <v>783</v>
+        <v>205</v>
       </c>
       <c r="AT246" t="s" s="2">
         <v>84</v>
@@ -36409,10 +36419,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -36420,7 +36430,7 @@
       </c>
       <c r="E247" s="2"/>
       <c r="F247" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G247" t="s" s="2">
         <v>102</v>
@@ -36438,10 +36448,10 @@
         <v>240</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>785</v>
+        <v>241</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>786</v>
+        <v>242</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -36468,13 +36478,11 @@
         <v>84</v>
       </c>
       <c r="X247" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y247" t="s" s="2">
-        <v>787</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>788</v>
+        <v>851</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>84</v>
@@ -36492,10 +36500,10 @@
         <v>84</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>784</v>
+        <v>245</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>102</v>
@@ -36531,10 +36539,10 @@
         <v>84</v>
       </c>
       <c r="AS247" t="s" s="2">
-        <v>770</v>
+        <v>205</v>
       </c>
       <c r="AT247" t="s" s="2">
-        <v>790</v>
+        <v>84</v>
       </c>
       <c r="AU247" t="s" s="2">
         <v>84</v>
@@ -36553,7 +36561,7 @@
       </c>
       <c r="E248" s="2"/>
       <c r="F248" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G248" t="s" s="2">
         <v>102</v>
@@ -36568,22 +36576,24 @@
         <v>84</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N248" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N248" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O248" s="2"/>
       <c r="P248" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q248" s="2"/>
       <c r="R248" t="s" s="2">
-        <v>84</v>
+        <v>854</v>
       </c>
       <c r="S248" t="s" s="2">
         <v>84</v>
@@ -36625,10 +36635,10 @@
         <v>84</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="AG248" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH248" t="s" s="2">
         <v>102</v>
@@ -36664,7 +36674,7 @@
         <v>84</v>
       </c>
       <c r="AS248" t="s" s="2">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="AT248" t="s" s="2">
         <v>84</v>
@@ -36675,21 +36685,21 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H249" t="s" s="2">
         <v>84</v>
@@ -36701,17 +36711,15 @@
         <v>84</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>123</v>
+        <v>314</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N249" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N249" s="2"/>
       <c r="O249" s="2"/>
       <c r="P249" t="s" s="2">
         <v>84</v>
@@ -36748,31 +36756,31 @@
         <v>84</v>
       </c>
       <c r="AB249" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC249" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD249" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE249" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH249" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI249" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ249" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK249" t="s" s="2">
         <v>84</v>
@@ -36799,7 +36807,7 @@
         <v>84</v>
       </c>
       <c r="AS249" t="s" s="2">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="AT249" t="s" s="2">
         <v>84</v>
@@ -36810,14 +36818,14 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>857</v>
+        <v>774</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
-        <v>84</v>
+        <v>775</v>
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
@@ -36830,25 +36838,25 @@
         <v>84</v>
       </c>
       <c r="I250" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J250" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>858</v>
+        <v>776</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>859</v>
+        <v>777</v>
       </c>
       <c r="N250" t="s" s="2">
-        <v>860</v>
+        <v>126</v>
       </c>
       <c r="O250" t="s" s="2">
-        <v>861</v>
+        <v>415</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>84</v>
@@ -36885,17 +36893,19 @@
         <v>84</v>
       </c>
       <c r="AB250" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AC250" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD250" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE250" t="s" s="2">
-        <v>862</v>
+        <v>84</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>863</v>
+        <v>778</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>85</v>
@@ -36907,7 +36917,7 @@
         <v>84</v>
       </c>
       <c r="AJ250" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK250" t="s" s="2">
         <v>84</v>
@@ -36931,10 +36941,10 @@
         <v>84</v>
       </c>
       <c r="AR250" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS250" t="s" s="2">
-        <v>865</v>
+        <v>205</v>
       </c>
       <c r="AT250" t="s" s="2">
         <v>84</v>
@@ -36943,16 +36953,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C251" t="s" s="2">
-        <v>867</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
         <v>84</v>
       </c>
@@ -36961,31 +36969,29 @@
         <v>85</v>
       </c>
       <c r="G251" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H251" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I251" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J251" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>160</v>
+        <v>418</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>858</v>
+        <v>780</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N251" t="s" s="2">
-        <v>860</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="N251" s="2"/>
       <c r="O251" t="s" s="2">
-        <v>861</v>
+        <v>782</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>84</v>
@@ -37010,11 +37016,13 @@
         <v>84</v>
       </c>
       <c r="X251" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y251" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y251" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z251" t="s" s="2">
-        <v>868</v>
+        <v>84</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>84</v>
@@ -37032,7 +37040,7 @@
         <v>84</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>863</v>
+        <v>779</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>85</v>
@@ -37068,10 +37076,10 @@
         <v>84</v>
       </c>
       <c r="AR251" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS251" t="s" s="2">
-        <v>865</v>
+        <v>783</v>
       </c>
       <c r="AT251" t="s" s="2">
         <v>84</v>
@@ -37080,50 +37088,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C252" t="s" s="2">
-        <v>802</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E252" s="2"/>
       <c r="F252" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G252" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H252" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I252" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J252" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>858</v>
+        <v>785</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N252" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O252" t="s" s="2">
-        <v>861</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="N252" s="2"/>
+      <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
         <v>84</v>
       </c>
@@ -37147,11 +37149,13 @@
         <v>84</v>
       </c>
       <c r="X252" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y252" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="Y252" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z252" t="s" s="2">
-        <v>870</v>
+        <v>788</v>
       </c>
       <c r="AA252" t="s" s="2">
         <v>84</v>
@@ -37169,13 +37173,13 @@
         <v>84</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>863</v>
+        <v>784</v>
       </c>
       <c r="AG252" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH252" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI252" t="s" s="2">
         <v>84</v>
@@ -37205,13 +37209,13 @@
         <v>84</v>
       </c>
       <c r="AR252" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS252" t="s" s="2">
-        <v>865</v>
+        <v>770</v>
       </c>
       <c r="AT252" t="s" s="2">
-        <v>84</v>
+        <v>790</v>
       </c>
       <c r="AU252" t="s" s="2">
         <v>84</v>
@@ -37219,10 +37223,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -37242,23 +37246,19 @@
         <v>84</v>
       </c>
       <c r="J253" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K253" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>873</v>
+        <v>117</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="O253" t="s" s="2">
-        <v>876</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N253" s="2"/>
+      <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
         <v>84</v>
       </c>
@@ -37306,7 +37306,7 @@
         <v>84</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>877</v>
+        <v>119</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>85</v>
@@ -37318,7 +37318,7 @@
         <v>84</v>
       </c>
       <c r="AJ253" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK253" t="s" s="2">
         <v>84</v>
@@ -37342,10 +37342,10 @@
         <v>84</v>
       </c>
       <c r="AR253" t="s" s="2">
-        <v>878</v>
+        <v>84</v>
       </c>
       <c r="AS253" t="s" s="2">
-        <v>879</v>
+        <v>120</v>
       </c>
       <c r="AT253" t="s" s="2">
         <v>84</v>
@@ -37356,21 +37356,21 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>791</v>
+        <v>863</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E254" s="2"/>
       <c r="F254" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G254" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H254" t="s" s="2">
         <v>84</v>
@@ -37382,18 +37382,18 @@
         <v>84</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>881</v>
+        <v>124</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N254" s="2"/>
-      <c r="O254" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N254" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O254" s="2"/>
       <c r="P254" t="s" s="2">
         <v>84</v>
       </c>
@@ -37429,31 +37429,31 @@
         <v>84</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC254" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD254" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>791</v>
+        <v>130</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI254" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ254" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK254" t="s" s="2">
         <v>84</v>
@@ -37480,10 +37480,10 @@
         <v>84</v>
       </c>
       <c r="AS254" t="s" s="2">
-        <v>795</v>
+        <v>120</v>
       </c>
       <c r="AT254" t="s" s="2">
-        <v>796</v>
+        <v>84</v>
       </c>
       <c r="AU254" t="s" s="2">
         <v>84</v>
@@ -37491,10 +37491,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -37505,7 +37505,7 @@
         <v>85</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>84</v>
@@ -37514,19 +37514,23 @@
         <v>84</v>
       </c>
       <c r="J255" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>117</v>
+        <v>866</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N255" s="2"/>
-      <c r="O255" s="2"/>
+        <v>867</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="O255" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P255" t="s" s="2">
         <v>84</v>
       </c>
@@ -37562,31 +37566,29 @@
         <v>84</v>
       </c>
       <c r="AB255" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC255" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AC255" s="2"/>
       <c r="AD255" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE255" t="s" s="2">
-        <v>84</v>
+        <v>870</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>119</v>
+        <v>871</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI255" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>84</v>
@@ -37610,10 +37612,10 @@
         <v>84</v>
       </c>
       <c r="AR255" t="s" s="2">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="AS255" t="s" s="2">
-        <v>120</v>
+        <v>873</v>
       </c>
       <c r="AT255" t="s" s="2">
         <v>84</v>
@@ -37622,46 +37624,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="256" hidden="true">
+    <row r="256">
       <c r="A256" t="s" s="2">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="C256" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>875</v>
+      </c>
       <c r="D256" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H256" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I256" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J256" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>124</v>
+        <v>866</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>125</v>
+        <v>867</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O256" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="O256" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P256" t="s" s="2">
         <v>84</v>
       </c>
@@ -37685,31 +37691,29 @@
         <v>84</v>
       </c>
       <c r="X256" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y256" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>84</v>
+        <v>876</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB256" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC256" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD256" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE256" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>130</v>
+        <v>871</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>85</v>
@@ -37721,7 +37725,7 @@
         <v>84</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>84</v>
@@ -37745,10 +37749,10 @@
         <v>84</v>
       </c>
       <c r="AR256" t="s" s="2">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="AS256" t="s" s="2">
-        <v>120</v>
+        <v>873</v>
       </c>
       <c r="AT256" t="s" s="2">
         <v>84</v>
@@ -37757,14 +37761,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="257" hidden="true">
+    <row r="257">
       <c r="A257" t="s" s="2">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="C257" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C257" t="s" s="2">
+        <v>802</v>
+      </c>
       <c r="D257" t="s" s="2">
         <v>84</v>
       </c>
@@ -37776,7 +37782,7 @@
         <v>102</v>
       </c>
       <c r="H257" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I257" t="s" s="2">
         <v>84</v>
@@ -37785,18 +37791,20 @@
         <v>103</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>269</v>
+        <v>867</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O257" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="O257" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P257" t="s" s="2">
         <v>84</v>
       </c>
@@ -37820,13 +37828,11 @@
         <v>84</v>
       </c>
       <c r="X257" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y257" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y257" s="2"/>
       <c r="Z257" t="s" s="2">
-        <v>84</v>
+        <v>878</v>
       </c>
       <c r="AA257" t="s" s="2">
         <v>84</v>
@@ -37844,16 +37850,16 @@
         <v>84</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>271</v>
+        <v>871</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>114</v>
@@ -37868,7 +37874,7 @@
         <v>84</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>889</v>
+        <v>84</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>84</v>
@@ -37880,10 +37886,10 @@
         <v>84</v>
       </c>
       <c r="AR257" t="s" s="2">
-        <v>274</v>
+        <v>872</v>
       </c>
       <c r="AS257" t="s" s="2">
-        <v>275</v>
+        <v>873</v>
       </c>
       <c r="AT257" t="s" s="2">
         <v>84</v>
@@ -37894,10 +37900,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -37920,24 +37926,24 @@
         <v>103</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>279</v>
+        <v>882</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O258" s="2"/>
+        <v>883</v>
+      </c>
+      <c r="O258" t="s" s="2">
+        <v>884</v>
+      </c>
       <c r="P258" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q258" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="Q258" s="2"/>
       <c r="R258" t="s" s="2">
         <v>84</v>
       </c>
@@ -37981,7 +37987,7 @@
         <v>84</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>282</v>
+        <v>885</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>85</v>
@@ -37990,7 +37996,7 @@
         <v>102</v>
       </c>
       <c r="AI258" t="s" s="2">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ258" t="s" s="2">
         <v>114</v>
@@ -38005,7 +38011,7 @@
         <v>84</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>893</v>
+        <v>84</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>84</v>
@@ -38017,10 +38023,10 @@
         <v>84</v>
       </c>
       <c r="AR258" t="s" s="2">
-        <v>284</v>
+        <v>886</v>
       </c>
       <c r="AS258" t="s" s="2">
-        <v>285</v>
+        <v>887</v>
       </c>
       <c r="AT258" t="s" s="2">
         <v>84</v>
@@ -38031,10 +38037,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -38057,16 +38063,18 @@
         <v>84</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>895</v>
+        <v>260</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="N259" s="2"/>
-      <c r="O259" s="2"/>
+      <c r="O259" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="P259" t="s" s="2">
         <v>84</v>
       </c>
@@ -38114,7 +38122,7 @@
         <v>84</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>85</v>
@@ -38138,7 +38146,7 @@
         <v>84</v>
       </c>
       <c r="AN259" t="s" s="2">
-        <v>897</v>
+        <v>84</v>
       </c>
       <c r="AO259" t="s" s="2">
         <v>84</v>
@@ -38153,10 +38161,10 @@
         <v>84</v>
       </c>
       <c r="AS259" t="s" s="2">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="AT259" t="s" s="2">
-        <v>84</v>
+        <v>796</v>
       </c>
       <c r="AU259" t="s" s="2">
         <v>84</v>
@@ -38164,14 +38172,12 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="C260" t="s" s="2">
-        <v>899</v>
-      </c>
+        <v>891</v>
+      </c>
+      <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
         <v>84</v>
       </c>
@@ -38192,13 +38198,13 @@
         <v>84</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>765</v>
+        <v>116</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>900</v>
+        <v>117</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>767</v>
+        <v>118</v>
       </c>
       <c r="N260" s="2"/>
       <c r="O260" s="2"/>
@@ -38249,19 +38255,19 @@
         <v>84</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>764</v>
+        <v>119</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH260" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI260" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ260" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK260" t="s" s="2">
         <v>84</v>
@@ -38285,13 +38291,13 @@
         <v>84</v>
       </c>
       <c r="AR260" t="s" s="2">
-        <v>769</v>
+        <v>84</v>
       </c>
       <c r="AS260" t="s" s="2">
-        <v>770</v>
+        <v>120</v>
       </c>
       <c r="AT260" t="s" s="2">
-        <v>771</v>
+        <v>84</v>
       </c>
       <c r="AU260" t="s" s="2">
         <v>84</v>
@@ -38299,21 +38305,21 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>772</v>
+        <v>893</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G261" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H261" t="s" s="2">
         <v>84</v>
@@ -38325,15 +38331,17 @@
         <v>84</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N261" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
         <v>84</v>
@@ -38370,31 +38378,31 @@
         <v>84</v>
       </c>
       <c r="AB261" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC261" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD261" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE261" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH261" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI261" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ261" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK261" t="s" s="2">
         <v>84</v>
@@ -38432,21 +38440,21 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>773</v>
+        <v>895</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G262" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H262" t="s" s="2">
         <v>84</v>
@@ -38455,19 +38463,19 @@
         <v>84</v>
       </c>
       <c r="J262" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>123</v>
+        <v>267</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>124</v>
+        <v>896</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="N262" t="s" s="2">
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="O262" s="2"/>
       <c r="P262" t="s" s="2">
@@ -38517,19 +38525,19 @@
         <v>84</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>130</v>
+        <v>271</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH262" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK262" t="s" s="2">
         <v>84</v>
@@ -38541,7 +38549,7 @@
         <v>84</v>
       </c>
       <c r="AN262" t="s" s="2">
-        <v>84</v>
+        <v>897</v>
       </c>
       <c r="AO262" t="s" s="2">
         <v>84</v>
@@ -38553,10 +38561,10 @@
         <v>84</v>
       </c>
       <c r="AR262" t="s" s="2">
-        <v>84</v>
+        <v>274</v>
       </c>
       <c r="AS262" t="s" s="2">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="AT262" t="s" s="2">
         <v>84</v>
@@ -38567,50 +38575,50 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>774</v>
+        <v>899</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
-        <v>775</v>
+        <v>84</v>
       </c>
       <c r="E263" s="2"/>
       <c r="F263" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H263" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I263" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J263" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>123</v>
+        <v>267</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>776</v>
+        <v>900</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>777</v>
+        <v>279</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O263" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q263" s="2"/>
+      <c r="Q263" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="R263" t="s" s="2">
         <v>84</v>
       </c>
@@ -38654,19 +38662,19 @@
         <v>84</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>778</v>
+        <v>282</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="AJ263" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK263" t="s" s="2">
         <v>84</v>
@@ -38678,7 +38686,7 @@
         <v>84</v>
       </c>
       <c r="AN263" t="s" s="2">
-        <v>84</v>
+        <v>901</v>
       </c>
       <c r="AO263" t="s" s="2">
         <v>84</v>
@@ -38690,10 +38698,10 @@
         <v>84</v>
       </c>
       <c r="AR263" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AS263" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="AT263" t="s" s="2">
         <v>84</v>
@@ -38704,10 +38712,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -38718,7 +38726,7 @@
         <v>85</v>
       </c>
       <c r="G264" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H264" t="s" s="2">
         <v>84</v>
@@ -38730,18 +38738,16 @@
         <v>84</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="N264" s="2"/>
-      <c r="O264" t="s" s="2">
-        <v>782</v>
-      </c>
+      <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
         <v>84</v>
       </c>
@@ -38789,13 +38795,13 @@
         <v>84</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH264" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI264" t="s" s="2">
         <v>84</v>
@@ -38828,7 +38834,7 @@
         <v>84</v>
       </c>
       <c r="AS264" t="s" s="2">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="AT264" t="s" s="2">
         <v>84</v>
@@ -38839,18 +38845,20 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="C265" s="2"/>
+        <v>764</v>
+      </c>
+      <c r="C265" t="s" s="2">
+        <v>904</v>
+      </c>
       <c r="D265" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G265" t="s" s="2">
         <v>102</v>
@@ -38865,13 +38873,13 @@
         <v>84</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>240</v>
+        <v>765</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>785</v>
+        <v>905</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="N265" s="2"/>
       <c r="O265" s="2"/>
@@ -38898,13 +38906,13 @@
         <v>84</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>787</v>
+        <v>84</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>788</v>
+        <v>84</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>84</v>
@@ -38922,13 +38930,13 @@
         <v>84</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="AG265" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH265" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI265" t="s" s="2">
         <v>84</v>
@@ -38958,13 +38966,13 @@
         <v>84</v>
       </c>
       <c r="AR265" t="s" s="2">
-        <v>84</v>
+        <v>769</v>
       </c>
       <c r="AS265" t="s" s="2">
         <v>770</v>
       </c>
       <c r="AT265" t="s" s="2">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AU265" t="s" s="2">
         <v>84</v>
@@ -38975,7 +38983,7 @@
         <v>906</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>853</v>
+        <v>772</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -39108,7 +39116,7 @@
         <v>907</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>855</v>
+        <v>773</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -39178,16 +39186,16 @@
         <v>84</v>
       </c>
       <c r="AB267" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC267" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD267" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF267" t="s" s="2">
         <v>130</v>
@@ -39243,11 +39251,11 @@
         <v>908</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>857</v>
+        <v>774</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
-        <v>84</v>
+        <v>775</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" t="s" s="2">
@@ -39260,25 +39268,25 @@
         <v>84</v>
       </c>
       <c r="I268" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J268" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>858</v>
+        <v>776</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>859</v>
+        <v>777</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>860</v>
+        <v>126</v>
       </c>
       <c r="O268" t="s" s="2">
-        <v>861</v>
+        <v>415</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>84</v>
@@ -39315,17 +39323,19 @@
         <v>84</v>
       </c>
       <c r="AB268" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AC268" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC268" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD268" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE268" t="s" s="2">
-        <v>862</v>
+        <v>84</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>863</v>
+        <v>778</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>85</v>
@@ -39337,7 +39347,7 @@
         <v>84</v>
       </c>
       <c r="AJ268" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK268" t="s" s="2">
         <v>84</v>
@@ -39361,10 +39371,10 @@
         <v>84</v>
       </c>
       <c r="AR268" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS268" t="s" s="2">
-        <v>865</v>
+        <v>205</v>
       </c>
       <c r="AT268" t="s" s="2">
         <v>84</v>
@@ -39373,16 +39383,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
         <v>909</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C269" t="s" s="2">
-        <v>910</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
         <v>84</v>
       </c>
@@ -39391,31 +39399,29 @@
         <v>85</v>
       </c>
       <c r="G269" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H269" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I269" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J269" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>160</v>
+        <v>418</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>911</v>
+        <v>780</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N269" t="s" s="2">
-        <v>860</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="N269" s="2"/>
       <c r="O269" t="s" s="2">
-        <v>861</v>
+        <v>782</v>
       </c>
       <c r="P269" t="s" s="2">
         <v>84</v>
@@ -39440,11 +39446,13 @@
         <v>84</v>
       </c>
       <c r="X269" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y269" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y269" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z269" t="s" s="2">
-        <v>912</v>
+        <v>84</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>84</v>
@@ -39462,7 +39470,7 @@
         <v>84</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>863</v>
+        <v>779</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>85</v>
@@ -39480,7 +39488,7 @@
         <v>84</v>
       </c>
       <c r="AL269" t="s" s="2">
-        <v>913</v>
+        <v>84</v>
       </c>
       <c r="AM269" t="s" s="2">
         <v>84</v>
@@ -39498,10 +39506,10 @@
         <v>84</v>
       </c>
       <c r="AR269" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS269" t="s" s="2">
-        <v>865</v>
+        <v>783</v>
       </c>
       <c r="AT269" t="s" s="2">
         <v>84</v>
@@ -39510,50 +39518,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C270" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G270" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H270" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I270" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J270" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>915</v>
+        <v>785</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N270" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O270" t="s" s="2">
-        <v>861</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="N270" s="2"/>
+      <c r="O270" s="2"/>
       <c r="P270" t="s" s="2">
         <v>84</v>
       </c>
@@ -39577,11 +39579,13 @@
         <v>84</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y270" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="Y270" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z270" t="s" s="2">
-        <v>916</v>
+        <v>788</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>84</v>
@@ -39599,13 +39603,13 @@
         <v>84</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>863</v>
+        <v>784</v>
       </c>
       <c r="AG270" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH270" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI270" t="s" s="2">
         <v>84</v>
@@ -39617,7 +39621,7 @@
         <v>84</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>917</v>
+        <v>84</v>
       </c>
       <c r="AM270" t="s" s="2">
         <v>84</v>
@@ -39635,13 +39639,13 @@
         <v>84</v>
       </c>
       <c r="AR270" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS270" t="s" s="2">
-        <v>865</v>
+        <v>770</v>
       </c>
       <c r="AT270" t="s" s="2">
-        <v>84</v>
+        <v>790</v>
       </c>
       <c r="AU270" t="s" s="2">
         <v>84</v>
@@ -39649,10 +39653,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -39672,23 +39676,19 @@
         <v>84</v>
       </c>
       <c r="J271" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K271" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>873</v>
+        <v>117</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="N271" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="O271" t="s" s="2">
-        <v>876</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N271" s="2"/>
+      <c r="O271" s="2"/>
       <c r="P271" t="s" s="2">
         <v>84</v>
       </c>
@@ -39736,7 +39736,7 @@
         <v>84</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>877</v>
+        <v>119</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>85</v>
@@ -39748,7 +39748,7 @@
         <v>84</v>
       </c>
       <c r="AJ271" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK271" t="s" s="2">
         <v>84</v>
@@ -39772,10 +39772,10 @@
         <v>84</v>
       </c>
       <c r="AR271" t="s" s="2">
-        <v>878</v>
+        <v>84</v>
       </c>
       <c r="AS271" t="s" s="2">
-        <v>879</v>
+        <v>120</v>
       </c>
       <c r="AT271" t="s" s="2">
         <v>84</v>
@@ -39784,26 +39784,26 @@
         <v>84</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>791</v>
+        <v>863</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G272" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H272" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I272" t="s" s="2">
         <v>84</v>
@@ -39812,18 +39812,18 @@
         <v>84</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>792</v>
+        <v>124</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N272" s="2"/>
-      <c r="O272" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
         <v>84</v>
       </c>
@@ -39859,31 +39859,31 @@
         <v>84</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC272" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD272" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>791</v>
+        <v>130</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH272" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI272" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK272" t="s" s="2">
         <v>84</v>
@@ -39910,10 +39910,10 @@
         <v>84</v>
       </c>
       <c r="AS272" t="s" s="2">
-        <v>795</v>
+        <v>120</v>
       </c>
       <c r="AT272" t="s" s="2">
-        <v>796</v>
+        <v>84</v>
       </c>
       <c r="AU272" t="s" s="2">
         <v>84</v>
@@ -39921,10 +39921,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -39935,7 +39935,7 @@
         <v>85</v>
       </c>
       <c r="G273" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H273" t="s" s="2">
         <v>84</v>
@@ -39944,19 +39944,23 @@
         <v>84</v>
       </c>
       <c r="J273" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>117</v>
+        <v>866</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N273" s="2"/>
-      <c r="O273" s="2"/>
+        <v>867</v>
+      </c>
+      <c r="N273" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="O273" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P273" t="s" s="2">
         <v>84</v>
       </c>
@@ -39992,31 +39996,29 @@
         <v>84</v>
       </c>
       <c r="AB273" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC273" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AC273" s="2"/>
       <c r="AD273" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE273" t="s" s="2">
-        <v>84</v>
+        <v>870</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>119</v>
+        <v>871</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH273" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI273" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>84</v>
@@ -40040,10 +40042,10 @@
         <v>84</v>
       </c>
       <c r="AR273" t="s" s="2">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="AS273" t="s" s="2">
-        <v>120</v>
+        <v>873</v>
       </c>
       <c r="AT273" t="s" s="2">
         <v>84</v>
@@ -40052,46 +40054,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="274" hidden="true">
+    <row r="274">
       <c r="A274" t="s" s="2">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="C274" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C274" t="s" s="2">
+        <v>915</v>
+      </c>
       <c r="D274" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H274" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I274" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J274" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>124</v>
+        <v>916</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>125</v>
+        <v>867</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O274" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="O274" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P274" t="s" s="2">
         <v>84</v>
       </c>
@@ -40115,31 +40121,29 @@
         <v>84</v>
       </c>
       <c r="X274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y274" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y274" s="2"/>
       <c r="Z274" t="s" s="2">
-        <v>84</v>
+        <v>917</v>
       </c>
       <c r="AA274" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB274" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC274" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD274" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE274" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>130</v>
+        <v>871</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>85</v>
@@ -40151,13 +40155,13 @@
         <v>84</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL274" t="s" s="2">
-        <v>84</v>
+        <v>918</v>
       </c>
       <c r="AM274" t="s" s="2">
         <v>84</v>
@@ -40175,10 +40179,10 @@
         <v>84</v>
       </c>
       <c r="AR274" t="s" s="2">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="AS274" t="s" s="2">
-        <v>120</v>
+        <v>873</v>
       </c>
       <c r="AT274" t="s" s="2">
         <v>84</v>
@@ -40187,14 +40191,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="275" hidden="true">
+    <row r="275">
       <c r="A275" t="s" s="2">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="C275" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C275" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="D275" t="s" s="2">
         <v>84</v>
       </c>
@@ -40206,7 +40212,7 @@
         <v>102</v>
       </c>
       <c r="H275" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I275" t="s" s="2">
         <v>84</v>
@@ -40215,18 +40221,20 @@
         <v>103</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>269</v>
+        <v>867</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O275" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="O275" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P275" t="s" s="2">
         <v>84</v>
       </c>
@@ -40250,13 +40258,11 @@
         <v>84</v>
       </c>
       <c r="X275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y275" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y275" s="2"/>
       <c r="Z275" t="s" s="2">
-        <v>84</v>
+        <v>921</v>
       </c>
       <c r="AA275" t="s" s="2">
         <v>84</v>
@@ -40274,16 +40280,16 @@
         <v>84</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>271</v>
+        <v>871</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH275" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ275" t="s" s="2">
         <v>114</v>
@@ -40292,7 +40298,7 @@
         <v>84</v>
       </c>
       <c r="AL275" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="AM275" t="s" s="2">
         <v>84</v>
@@ -40310,10 +40316,10 @@
         <v>84</v>
       </c>
       <c r="AR275" t="s" s="2">
-        <v>274</v>
+        <v>872</v>
       </c>
       <c r="AS275" t="s" s="2">
-        <v>275</v>
+        <v>873</v>
       </c>
       <c r="AT275" t="s" s="2">
         <v>84</v>
@@ -40324,10 +40330,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -40350,24 +40356,24 @@
         <v>103</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>926</v>
+        <v>881</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>279</v>
+        <v>882</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O276" s="2"/>
+        <v>883</v>
+      </c>
+      <c r="O276" t="s" s="2">
+        <v>884</v>
+      </c>
       <c r="P276" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q276" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="Q276" s="2"/>
       <c r="R276" t="s" s="2">
         <v>84</v>
       </c>
@@ -40411,7 +40417,7 @@
         <v>84</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>282</v>
+        <v>885</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>85</v>
@@ -40420,7 +40426,7 @@
         <v>102</v>
       </c>
       <c r="AI276" t="s" s="2">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ276" t="s" s="2">
         <v>114</v>
@@ -40429,7 +40435,7 @@
         <v>84</v>
       </c>
       <c r="AL276" t="s" s="2">
-        <v>927</v>
+        <v>84</v>
       </c>
       <c r="AM276" t="s" s="2">
         <v>84</v>
@@ -40447,10 +40453,10 @@
         <v>84</v>
       </c>
       <c r="AR276" t="s" s="2">
-        <v>284</v>
+        <v>886</v>
       </c>
       <c r="AS276" t="s" s="2">
-        <v>285</v>
+        <v>887</v>
       </c>
       <c r="AT276" t="s" s="2">
         <v>84</v>
@@ -40459,12 +40465,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="277" hidden="true">
+    <row r="277">
       <c r="A277" t="s" s="2">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -40478,7 +40484,7 @@
         <v>102</v>
       </c>
       <c r="H277" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I277" t="s" s="2">
         <v>84</v>
@@ -40487,16 +40493,18 @@
         <v>84</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>474</v>
+        <v>260</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="N277" s="2"/>
-      <c r="O277" s="2"/>
+      <c r="O277" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="P277" t="s" s="2">
         <v>84</v>
       </c>
@@ -40544,7 +40552,7 @@
         <v>84</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>85</v>
@@ -40583,10 +40591,10 @@
         <v>84</v>
       </c>
       <c r="AS277" t="s" s="2">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="AT277" t="s" s="2">
-        <v>84</v>
+        <v>796</v>
       </c>
       <c r="AU277" t="s" s="2">
         <v>84</v>
@@ -40594,14 +40602,12 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="C278" t="s" s="2">
-        <v>930</v>
-      </c>
+        <v>891</v>
+      </c>
+      <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
         <v>84</v>
       </c>
@@ -40610,7 +40616,7 @@
         <v>85</v>
       </c>
       <c r="G278" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H278" t="s" s="2">
         <v>84</v>
@@ -40622,13 +40628,13 @@
         <v>84</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>765</v>
+        <v>116</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>931</v>
+        <v>117</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>767</v>
+        <v>118</v>
       </c>
       <c r="N278" s="2"/>
       <c r="O278" s="2"/>
@@ -40679,19 +40685,19 @@
         <v>84</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>764</v>
+        <v>119</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH278" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI278" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ278" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK278" t="s" s="2">
         <v>84</v>
@@ -40715,13 +40721,13 @@
         <v>84</v>
       </c>
       <c r="AR278" t="s" s="2">
-        <v>769</v>
+        <v>84</v>
       </c>
       <c r="AS278" t="s" s="2">
-        <v>770</v>
+        <v>120</v>
       </c>
       <c r="AT278" t="s" s="2">
-        <v>771</v>
+        <v>84</v>
       </c>
       <c r="AU278" t="s" s="2">
         <v>84</v>
@@ -40729,21 +40735,21 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>772</v>
+        <v>893</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E279" s="2"/>
       <c r="F279" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G279" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H279" t="s" s="2">
         <v>84</v>
@@ -40755,15 +40761,17 @@
         <v>84</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N279" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N279" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
         <v>84</v>
@@ -40800,31 +40808,31 @@
         <v>84</v>
       </c>
       <c r="AB279" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC279" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD279" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE279" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI279" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ279" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK279" t="s" s="2">
         <v>84</v>
@@ -40862,21 +40870,21 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>773</v>
+        <v>895</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E280" s="2"/>
       <c r="F280" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G280" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H280" t="s" s="2">
         <v>84</v>
@@ -40885,19 +40893,19 @@
         <v>84</v>
       </c>
       <c r="J280" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>123</v>
+        <v>267</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>124</v>
+        <v>928</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>125</v>
+        <v>269</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" t="s" s="2">
@@ -40947,25 +40955,25 @@
         <v>84</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>130</v>
+        <v>271</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH280" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="AJ280" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK280" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL280" t="s" s="2">
-        <v>84</v>
+        <v>929</v>
       </c>
       <c r="AM280" t="s" s="2">
         <v>84</v>
@@ -40983,10 +40991,10 @@
         <v>84</v>
       </c>
       <c r="AR280" t="s" s="2">
-        <v>84</v>
+        <v>274</v>
       </c>
       <c r="AS280" t="s" s="2">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="AT280" t="s" s="2">
         <v>84</v>
@@ -40997,50 +41005,50 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>774</v>
+        <v>899</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
-        <v>775</v>
+        <v>84</v>
       </c>
       <c r="E281" s="2"/>
       <c r="F281" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H281" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I281" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J281" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>123</v>
+        <v>267</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>776</v>
+        <v>931</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>777</v>
+        <v>279</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O281" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q281" s="2"/>
+      <c r="Q281" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="R281" t="s" s="2">
         <v>84</v>
       </c>
@@ -41084,25 +41092,25 @@
         <v>84</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>778</v>
+        <v>282</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH281" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="AJ281" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK281" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL281" t="s" s="2">
-        <v>84</v>
+        <v>932</v>
       </c>
       <c r="AM281" t="s" s="2">
         <v>84</v>
@@ -41120,10 +41128,10 @@
         <v>84</v>
       </c>
       <c r="AR281" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AS281" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="AT281" t="s" s="2">
         <v>84</v>
@@ -41134,10 +41142,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -41148,7 +41156,7 @@
         <v>85</v>
       </c>
       <c r="G282" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H282" t="s" s="2">
         <v>84</v>
@@ -41160,18 +41168,16 @@
         <v>84</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="N282" s="2"/>
-      <c r="O282" t="s" s="2">
-        <v>782</v>
-      </c>
+      <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
         <v>84</v>
       </c>
@@ -41219,13 +41225,13 @@
         <v>84</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH282" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI282" t="s" s="2">
         <v>84</v>
@@ -41258,7 +41264,7 @@
         <v>84</v>
       </c>
       <c r="AS282" t="s" s="2">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="AT282" t="s" s="2">
         <v>84</v>
@@ -41269,21 +41275,23 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="C283" s="2"/>
+        <v>764</v>
+      </c>
+      <c r="C283" t="s" s="2">
+        <v>935</v>
+      </c>
       <c r="D283" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E283" s="2"/>
       <c r="F283" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G283" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>84</v>
@@ -41295,13 +41303,13 @@
         <v>84</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>240</v>
+        <v>765</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>785</v>
+        <v>936</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -41328,13 +41336,13 @@
         <v>84</v>
       </c>
       <c r="X283" t="s" s="2">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="Y283" t="s" s="2">
-        <v>787</v>
+        <v>84</v>
       </c>
       <c r="Z283" t="s" s="2">
-        <v>788</v>
+        <v>84</v>
       </c>
       <c r="AA283" t="s" s="2">
         <v>84</v>
@@ -41352,13 +41360,13 @@
         <v>84</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="AG283" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH283" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI283" t="s" s="2">
         <v>84</v>
@@ -41367,7 +41375,7 @@
         <v>114</v>
       </c>
       <c r="AK283" t="s" s="2">
-        <v>937</v>
+        <v>84</v>
       </c>
       <c r="AL283" t="s" s="2">
         <v>84</v>
@@ -41388,13 +41396,13 @@
         <v>84</v>
       </c>
       <c r="AR283" t="s" s="2">
-        <v>84</v>
+        <v>769</v>
       </c>
       <c r="AS283" t="s" s="2">
         <v>770</v>
       </c>
       <c r="AT283" t="s" s="2">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AU283" t="s" s="2">
         <v>84</v>
@@ -41402,10 +41410,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>853</v>
+        <v>772</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -41535,10 +41543,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>855</v>
+        <v>773</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -41608,16 +41616,16 @@
         <v>84</v>
       </c>
       <c r="AB285" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC285" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD285" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE285" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF285" t="s" s="2">
         <v>130</v>
@@ -41670,14 +41678,14 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>857</v>
+        <v>774</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
-        <v>84</v>
+        <v>775</v>
       </c>
       <c r="E286" s="2"/>
       <c r="F286" t="s" s="2">
@@ -41690,25 +41698,25 @@
         <v>84</v>
       </c>
       <c r="I286" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J286" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>858</v>
+        <v>776</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>859</v>
+        <v>777</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>860</v>
+        <v>126</v>
       </c>
       <c r="O286" t="s" s="2">
-        <v>861</v>
+        <v>415</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>84</v>
@@ -41745,17 +41753,19 @@
         <v>84</v>
       </c>
       <c r="AB286" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AC286" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC286" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD286" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE286" t="s" s="2">
-        <v>862</v>
+        <v>84</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>863</v>
+        <v>778</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>85</v>
@@ -41767,7 +41777,7 @@
         <v>84</v>
       </c>
       <c r="AJ286" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK286" t="s" s="2">
         <v>84</v>
@@ -41791,10 +41801,10 @@
         <v>84</v>
       </c>
       <c r="AR286" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS286" t="s" s="2">
-        <v>865</v>
+        <v>205</v>
       </c>
       <c r="AT286" t="s" s="2">
         <v>84</v>
@@ -41803,16 +41813,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C287" t="s" s="2">
-        <v>942</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
         <v>84</v>
       </c>
@@ -41821,31 +41829,29 @@
         <v>85</v>
       </c>
       <c r="G287" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H287" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I287" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J287" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>160</v>
+        <v>418</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>943</v>
+        <v>780</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N287" t="s" s="2">
-        <v>860</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="N287" s="2"/>
       <c r="O287" t="s" s="2">
-        <v>861</v>
+        <v>782</v>
       </c>
       <c r="P287" t="s" s="2">
         <v>84</v>
@@ -41870,11 +41876,13 @@
         <v>84</v>
       </c>
       <c r="X287" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y287" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y287" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z287" t="s" s="2">
-        <v>944</v>
+        <v>84</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>84</v>
@@ -41892,7 +41900,7 @@
         <v>84</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>863</v>
+        <v>779</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>85</v>
@@ -41907,7 +41915,7 @@
         <v>114</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>945</v>
+        <v>84</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>84</v>
@@ -41928,10 +41936,10 @@
         <v>84</v>
       </c>
       <c r="AR287" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS287" t="s" s="2">
-        <v>865</v>
+        <v>783</v>
       </c>
       <c r="AT287" t="s" s="2">
         <v>84</v>
@@ -41940,50 +41948,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C288" t="s" s="2">
-        <v>930</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E288" s="2"/>
       <c r="F288" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G288" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H288" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I288" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J288" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>947</v>
+        <v>785</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N288" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O288" t="s" s="2">
-        <v>861</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="N288" s="2"/>
+      <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
         <v>84</v>
       </c>
@@ -42007,11 +42009,13 @@
         <v>84</v>
       </c>
       <c r="X288" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y288" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="Y288" t="s" s="2">
+        <v>787</v>
+      </c>
       <c r="Z288" t="s" s="2">
-        <v>948</v>
+        <v>788</v>
       </c>
       <c r="AA288" t="s" s="2">
         <v>84</v>
@@ -42029,13 +42033,13 @@
         <v>84</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>863</v>
+        <v>784</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH288" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI288" t="s" s="2">
         <v>84</v>
@@ -42044,7 +42048,7 @@
         <v>114</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>84</v>
+        <v>942</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>84</v>
@@ -42065,13 +42069,13 @@
         <v>84</v>
       </c>
       <c r="AR288" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AS288" t="s" s="2">
-        <v>865</v>
+        <v>770</v>
       </c>
       <c r="AT288" t="s" s="2">
-        <v>84</v>
+        <v>790</v>
       </c>
       <c r="AU288" t="s" s="2">
         <v>84</v>
@@ -42079,10 +42083,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -42102,23 +42106,19 @@
         <v>84</v>
       </c>
       <c r="J289" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K289" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>873</v>
+        <v>117</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="N289" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="O289" t="s" s="2">
-        <v>876</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N289" s="2"/>
+      <c r="O289" s="2"/>
       <c r="P289" t="s" s="2">
         <v>84</v>
       </c>
@@ -42166,7 +42166,7 @@
         <v>84</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>877</v>
+        <v>119</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>85</v>
@@ -42178,7 +42178,7 @@
         <v>84</v>
       </c>
       <c r="AJ289" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK289" t="s" s="2">
         <v>84</v>
@@ -42202,10 +42202,10 @@
         <v>84</v>
       </c>
       <c r="AR289" t="s" s="2">
-        <v>878</v>
+        <v>84</v>
       </c>
       <c r="AS289" t="s" s="2">
-        <v>879</v>
+        <v>120</v>
       </c>
       <c r="AT289" t="s" s="2">
         <v>84</v>
@@ -42216,21 +42216,21 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>791</v>
+        <v>863</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G290" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H290" t="s" s="2">
         <v>84</v>
@@ -42242,18 +42242,18 @@
         <v>84</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>792</v>
+        <v>124</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N290" s="2"/>
-      <c r="O290" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N290" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
         <v>84</v>
       </c>
@@ -42289,31 +42289,31 @@
         <v>84</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC290" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD290" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE290" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>791</v>
+        <v>130</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH290" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI290" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>84</v>
@@ -42340,10 +42340,10 @@
         <v>84</v>
       </c>
       <c r="AS290" t="s" s="2">
-        <v>795</v>
+        <v>120</v>
       </c>
       <c r="AT290" t="s" s="2">
-        <v>796</v>
+        <v>84</v>
       </c>
       <c r="AU290" t="s" s="2">
         <v>84</v>
@@ -42351,10 +42351,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -42365,7 +42365,7 @@
         <v>85</v>
       </c>
       <c r="G291" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H291" t="s" s="2">
         <v>84</v>
@@ -42374,19 +42374,23 @@
         <v>84</v>
       </c>
       <c r="J291" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K291" t="s" s="2">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>117</v>
+        <v>866</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N291" s="2"/>
-      <c r="O291" s="2"/>
+        <v>867</v>
+      </c>
+      <c r="N291" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="O291" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P291" t="s" s="2">
         <v>84</v>
       </c>
@@ -42422,31 +42426,29 @@
         <v>84</v>
       </c>
       <c r="AB291" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC291" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AC291" s="2"/>
       <c r="AD291" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE291" t="s" s="2">
-        <v>84</v>
+        <v>870</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>119</v>
+        <v>871</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH291" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI291" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ291" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK291" t="s" s="2">
         <v>84</v>
@@ -42470,10 +42472,10 @@
         <v>84</v>
       </c>
       <c r="AR291" t="s" s="2">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="AS291" t="s" s="2">
-        <v>120</v>
+        <v>873</v>
       </c>
       <c r="AT291" t="s" s="2">
         <v>84</v>
@@ -42482,46 +42484,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="292" hidden="true">
+    <row r="292">
       <c r="A292" t="s" s="2">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="C292" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C292" t="s" s="2">
+        <v>947</v>
+      </c>
       <c r="D292" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G292" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H292" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I292" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J292" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>124</v>
+        <v>948</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>125</v>
+        <v>867</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O292" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="O292" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P292" t="s" s="2">
         <v>84</v>
       </c>
@@ -42545,31 +42551,29 @@
         <v>84</v>
       </c>
       <c r="X292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y292" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>84</v>
+        <v>949</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB292" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC292" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD292" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE292" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>130</v>
+        <v>871</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>85</v>
@@ -42581,10 +42585,10 @@
         <v>84</v>
       </c>
       <c r="AJ292" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK292" t="s" s="2">
-        <v>84</v>
+        <v>950</v>
       </c>
       <c r="AL292" t="s" s="2">
         <v>84</v>
@@ -42605,10 +42609,10 @@
         <v>84</v>
       </c>
       <c r="AR292" t="s" s="2">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="AS292" t="s" s="2">
-        <v>120</v>
+        <v>873</v>
       </c>
       <c r="AT292" t="s" s="2">
         <v>84</v>
@@ -42617,14 +42621,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="293" hidden="true">
+    <row r="293">
       <c r="A293" t="s" s="2">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="C293" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="C293" t="s" s="2">
+        <v>935</v>
+      </c>
       <c r="D293" t="s" s="2">
         <v>84</v>
       </c>
@@ -42636,7 +42642,7 @@
         <v>102</v>
       </c>
       <c r="H293" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I293" t="s" s="2">
         <v>84</v>
@@ -42645,18 +42651,20 @@
         <v>103</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>269</v>
+        <v>867</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O293" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="O293" t="s" s="2">
+        <v>869</v>
+      </c>
       <c r="P293" t="s" s="2">
         <v>84</v>
       </c>
@@ -42680,13 +42688,11 @@
         <v>84</v>
       </c>
       <c r="X293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y293" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>84</v>
+        <v>953</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>84</v>
@@ -42704,22 +42710,22 @@
         <v>84</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>271</v>
+        <v>871</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH293" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>114</v>
       </c>
       <c r="AK293" t="s" s="2">
-        <v>955</v>
+        <v>84</v>
       </c>
       <c r="AL293" t="s" s="2">
         <v>84</v>
@@ -42740,10 +42746,10 @@
         <v>84</v>
       </c>
       <c r="AR293" t="s" s="2">
-        <v>274</v>
+        <v>872</v>
       </c>
       <c r="AS293" t="s" s="2">
-        <v>275</v>
+        <v>873</v>
       </c>
       <c r="AT293" t="s" s="2">
         <v>84</v>
@@ -42754,10 +42760,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -42780,24 +42786,24 @@
         <v>103</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>957</v>
+        <v>881</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>279</v>
+        <v>882</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O294" s="2"/>
+        <v>883</v>
+      </c>
+      <c r="O294" t="s" s="2">
+        <v>884</v>
+      </c>
       <c r="P294" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q294" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="Q294" s="2"/>
       <c r="R294" t="s" s="2">
         <v>84</v>
       </c>
@@ -42841,7 +42847,7 @@
         <v>84</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>282</v>
+        <v>885</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>85</v>
@@ -42850,13 +42856,13 @@
         <v>102</v>
       </c>
       <c r="AI294" t="s" s="2">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ294" t="s" s="2">
         <v>114</v>
       </c>
       <c r="AK294" t="s" s="2">
-        <v>958</v>
+        <v>84</v>
       </c>
       <c r="AL294" t="s" s="2">
         <v>84</v>
@@ -42877,10 +42883,10 @@
         <v>84</v>
       </c>
       <c r="AR294" t="s" s="2">
-        <v>284</v>
+        <v>886</v>
       </c>
       <c r="AS294" t="s" s="2">
-        <v>285</v>
+        <v>887</v>
       </c>
       <c r="AT294" t="s" s="2">
         <v>84</v>
@@ -42891,10 +42897,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -42917,16 +42923,18 @@
         <v>84</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>474</v>
+        <v>260</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="N295" s="2"/>
-      <c r="O295" s="2"/>
+      <c r="O295" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="P295" t="s" s="2">
         <v>84</v>
       </c>
@@ -42974,7 +42982,7 @@
         <v>84</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>85</v>
@@ -43013,21 +43021,21 @@
         <v>84</v>
       </c>
       <c r="AS295" t="s" s="2">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="AT295" t="s" s="2">
-        <v>84</v>
+        <v>796</v>
       </c>
       <c r="AU295" t="s" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>960</v>
+        <v>891</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -43038,10 +43046,10 @@
         <v>85</v>
       </c>
       <c r="G296" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H296" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I296" t="s" s="2">
         <v>84</v>
@@ -43050,20 +43058,16 @@
         <v>84</v>
       </c>
       <c r="K296" t="s" s="2">
-        <v>961</v>
+        <v>116</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>962</v>
+        <v>117</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>963</v>
-      </c>
-      <c r="N296" t="s" s="2">
-        <v>964</v>
-      </c>
-      <c r="O296" t="s" s="2">
-        <v>965</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N296" s="2"/>
+      <c r="O296" s="2"/>
       <c r="P296" t="s" s="2">
         <v>84</v>
       </c>
@@ -43087,78 +43091,755 @@
         <v>84</v>
       </c>
       <c r="X296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF296" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG296" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH296" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS296" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT296" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU296" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="297" hidden="true">
+      <c r="A297" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="C297" s="2"/>
+      <c r="D297" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E297" s="2"/>
+      <c r="F297" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G297" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K297" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L297" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M297" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N297" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O297" s="2"/>
+      <c r="P297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q297" s="2"/>
+      <c r="R297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB297" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AC297" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AD297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE297" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AF297" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG297" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH297" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ297" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS297" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT297" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU297" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="298" hidden="true">
+      <c r="A298" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="C298" s="2"/>
+      <c r="D298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E298" s="2"/>
+      <c r="F298" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G298" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J298" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K298" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L298" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="M298" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N298" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O298" s="2"/>
+      <c r="P298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q298" s="2"/>
+      <c r="R298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF298" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG298" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH298" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI298" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AJ298" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK298" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="AL298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR298" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AS298" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AT298" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU298" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="299" hidden="true">
+      <c r="A299" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="D299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E299" s="2"/>
+      <c r="F299" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G299" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J299" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K299" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L299" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="M299" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N299" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O299" s="2"/>
+      <c r="P299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q299" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="R299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF299" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG299" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH299" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI299" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AJ299" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK299" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="AL299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR299" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AS299" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AT299" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU299" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="300" hidden="true">
+      <c r="A300" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="C300" s="2"/>
+      <c r="D300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E300" s="2"/>
+      <c r="F300" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G300" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K300" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L300" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="M300" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="N300" s="2"/>
+      <c r="O300" s="2"/>
+      <c r="P300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q300" s="2"/>
+      <c r="R300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF300" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="AG300" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH300" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ300" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS300" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AT300" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU300" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="C301" s="2"/>
+      <c r="D301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E301" s="2"/>
+      <c r="F301" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G301" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H301" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K301" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="L301" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="M301" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="N301" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="O301" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="P301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q301" s="2"/>
+      <c r="R301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X301" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="Y296" s="2"/>
-      <c r="Z296" t="s" s="2">
-        <v>966</v>
-      </c>
-      <c r="AA296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF296" t="s" s="2">
-        <v>960</v>
-      </c>
-      <c r="AG296" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH296" t="s" s="2">
+      <c r="Y301" s="2"/>
+      <c r="Z301" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AA301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF301" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="AG301" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH301" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AI296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ296" t="s" s="2">
+      <c r="AI301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ301" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AK296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ296" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR296" t="s" s="2">
-        <v>967</v>
-      </c>
-      <c r="AS296" t="s" s="2">
-        <v>968</v>
-      </c>
-      <c r="AT296" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="AU296" t="s" s="2">
+      <c r="AK301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ301" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR301" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="AS301" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="AT301" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="AU301" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU296">
+  <autoFilter ref="A1:AU301">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -43168,7 +43849,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI295">
+  <conditionalFormatting sqref="A2:AI300">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,7 +695,7 @@
     <t>as-ext-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1001,7 +1001,7 @@
     <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1143,7 +1143,7 @@
     <t>as-ext-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2066,7 +2066,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2130,7 +2130,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2288,7 +2288,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2530,7 +2530,7 @@
     <t>as-ext-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -3004,7 +3004,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-2}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-3}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
